--- a/analysis/breakeven_model.xlsx
+++ b/analysis/breakeven_model.xlsx
@@ -8,9 +8,11 @@
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Assumptions" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Breakeven" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Sensitivity" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Inputs" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Capital" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Breakeven" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Commodity" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Compare" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,11 +21,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="166" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -47,8 +50,12 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="009C0006"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -68,6 +75,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
     <fill>
@@ -102,24 +114,34 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="2" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -485,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A30"/>
+  <dimension ref="A1:A33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -494,7 +516,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Oaxaca–Puebla Rail — Breakeven Model</t>
+          <t>Vía Corta Oaxaca — Freight Reactivation Breakeven Model</t>
         </is>
       </c>
     </row>
@@ -504,7 +526,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Status: Phase 0 scaffold. All inputs are blank. No breakeven figure has been established.</t>
+          <t>Puebla (Sánchez) → Oaxaca City, línea E, ~216.5 route-km. Screening level.</t>
         </is>
       </c>
     </row>
@@ -514,28 +536,28 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>PURPOSE</t>
+          <t>WHAT THIS MODEL DOES</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Answer one question: how many passengers a year does this line need to cover its costs,</t>
+          <t>Back-solves the annual tonnage required to break even, then expresses it as loaded</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>and how does that compare with the number of people who currently travel the corridor at all?</t>
+          <t>truckloads/day each way so it is directly comparable to observed road traffic.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>That comparison is stop rule SR-2 in deliverables/feasibility_screen.md.</t>
+          <t>It does NOT forecast demand.</t>
         </is>
       </c>
     </row>
@@ -545,131 +567,152 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>HOW TO USE</t>
+          <t>CELL COLOURS</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1. Fill a yellow input cell on 'Assumptions' ONLY together with its Source column entry.</t>
+          <t xml:space="preserve">  Yellow  = input, enter with a source</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   The source is the manifest ID from deliverables/data_sources.md, e.g. inegi-2020-censo.</t>
+          <t xml:space="preserve">  Orange  = ASSUMPTION with no primary source behind it — the honest label, not a value</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2. Green cells are calculated. Do not type over them.</t>
+          <t xml:space="preserve">  Green   = calculated, do not overtype</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>3. Blank inputs propagate as blank, not as zero — the model stays silent until it is fed.</t>
-        </is>
-      </c>
+      <c r="A14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>4. Read 'Breakeven'. Read 'Sensitivity' before believing 'Breakeven'.</t>
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>THE TWO NUMBERS THAT CARRY THE ANSWER</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr"/>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>1. Contribution margin per ton-km. Not public at commodity level; ARTF's Anuario was</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>CONVENTIONS</t>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   unreachable. It is therefore SWEPT across a range on 'Breakeven', not assumed.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Currency and base year are declared on 'Assumptions' and apply to every money figure.</t>
+          <t>2. Track condition. Unknown since 2003 and unresolvable from a desk, so capital is</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Mixing nominal and real figures, or MXN and USD, is risk R-10 in the risk register.</t>
+          <t xml:space="preserve">   presented as light / heavy / substantial reconstruction. If those straddle the</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr"/>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   breakeven threshold, STOP RULE 3 fires and the answer is INDETERMINATE.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>WHAT THIS MODEL DELIBERATELY DOES NOT DO</t>
-        </is>
-      </c>
+      <c r="A21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>It does not forecast demand. Projected ridership is corridor travel × an assumed capture</t>
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>O&amp;M CIRCULARITY</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>rate that the analyst enters by hand; the model reports what that assumption implies,</t>
+          <t>Track maintenance scales with gross passing tonnage, so O&amp;M depends on the tonnage</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>it does not defend it. Capital recovery is shown separately from operating breakeven</t>
+          <t>being solved for. Both revenue and variable O&amp;M are linear in tonnage, so the</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>because the funding model is unknown at screen stage — a line may be worth operating</t>
+          <t>circularity closes algebraically (see 'Breakeven' col A note) rather than by iteration.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>while never recovering its capital, and the screen should be able to say so.</t>
+          <t>If net contribution after track wear goes &lt;= 0, NO tonnage breaks even and the sheet</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr"/>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>reports that instead of a large finite number.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>It is a screening tool. Its output supports a decision to study further, nothing more.</t>
-        </is>
-      </c>
+      <c r="A28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr"/>
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>CURRENCY</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Regenerate with: python3 analysis/scripts/build_breakeven_model.py</t>
+          <t>One base year, stated on 'Inputs'. MXN throughout. Any USD conversion states its rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>and date. Mixing nominal figures across years is risk R-10.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Regenerate: python3 analysis/scripts/build_breakeven_model.py</t>
         </is>
       </c>
     </row>
@@ -684,27 +727,27 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="74" customWidth="1" min="5" max="5"/>
+    <col width="78" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Assumptions — all values pending Phase 2</t>
+          <t>Inputs — single editable block</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Yellow = enter a value with its source. Green = calculated. Never fill a value without a source.</t>
+          <t>Every downstream sheet reads from here. Orange = assumption with no primary source.</t>
         </is>
       </c>
     </row>
@@ -726,7 +769,7 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Source (manifest ID)</t>
+          <t>Source</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -745,6 +788,7 @@
       <c r="C4" s="6" t="n"/>
       <c r="D4" s="6" t="n"/>
       <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -752,34 +796,41 @@
           <t>Route length</t>
         </is>
       </c>
-      <c r="B5" s="7" t="n"/>
+      <c r="B5" s="7" t="n">
+        <v>216.5</v>
+      </c>
       <c r="C5" t="inlineStr">
         <is>
           <t>km</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Prompt.md (to verify)</t>
+        </is>
+      </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Plausible alignment, not straight-line distance</t>
+          <t>km E-150+000 to E-367+000. Independent verification outstanding</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>CAPITAL</t>
+          <t>CAPITAL — cost per route-km by track-condition scenario</t>
         </is>
       </c>
       <c r="B6" s="6" t="n"/>
       <c r="C6" s="6" t="n"/>
       <c r="D6" s="6" t="n"/>
       <c r="E6" s="6" t="n"/>
+      <c r="F6" s="6" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Capital cost per route-km</t>
+          <t>Light rehabilitation</t>
         </is>
       </c>
       <c r="B7" s="8" t="n"/>
@@ -791,23 +842,20 @@
       <c r="D7" t="inlineStr"/>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>[ANALOGUE] — only from a project of comparable terrain class</t>
+          <t>UNESCAP guidance cited in brief: &lt; USD 500,000/route-km. Convert at B26 and cite</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total capital cost</t>
-        </is>
-      </c>
-      <c r="B8" s="9">
-        <f>IF(OR(B5="",B7=""),"",B5*B7)</f>
-        <v/>
-      </c>
+          <t>Heavy rehabilitation</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="n"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MXN million</t>
+          <t>MXN million / km</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -816,352 +864,425 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Discount rate</t>
-        </is>
-      </c>
-      <c r="B9" s="10" t="n"/>
+          <t>Substantial reconstruction</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="n"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>% / yr</t>
+          <t>MXN million / km</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>Social discount rate used for public projects</t>
-        </is>
-      </c>
+      <c r="E9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Asset life</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="n"/>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>years</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" s="3" t="inlineStr"/>
+          <t xml:space="preserve">  Mexican precedent (context, NOT a base case)</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="n"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>[PRESS — UNVERIFIED]</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Press reports ~18,000 MXN million on Línea Z rehabilitation (~300 km) =&gt; order ~60 MXN million/km, roughly an order of magnitude above the UNESCAP figure. ASF primary unreachable (JS app), DOF egress-blocked. Must NOT carry a conclusion.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Annualised capital charge</t>
-        </is>
-      </c>
-      <c r="B11" s="9">
-        <f>IF(OR(B8="",B9="",B10=""),"",-PMT(B9,B10,B8))</f>
-        <v/>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>MXN million / yr</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>Level annual charge recovering capital over asset life</t>
-        </is>
-      </c>
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>CAPITAL — structures carried separately, per the brief</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n"/>
+      <c r="C11" s="6" t="n"/>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>OPERATING</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="n"/>
-      <c r="C12" s="6" t="n"/>
-      <c r="D12" s="6" t="n"/>
-      <c r="E12" s="6" t="n"/>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Bridges / drainage / slope stabilisation — low</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="n"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>MXN million</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Dominant uncertainty. Carried as its own line with its own range, NOT buried in a percentage contingency. No public structure inventory is expected to exist</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Daily services each way</t>
+          <t>Bridges / drainage / slope stabilisation — high</t>
         </is>
       </c>
       <c r="B13" s="7" t="n"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>trains / day</t>
+          <t>MXN million</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" s="3" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Operating days per year</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="n"/>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>days</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" s="3" t="inlineStr"/>
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>FINANCE</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Annual train-km</t>
-        </is>
-      </c>
-      <c r="B15" s="11">
-        <f>IF(OR(B5="",B13="",B14=""),"",B13*2*B14*B5)</f>
-        <v/>
+          <t>Asset life</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="n">
+        <v>30</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>train-km / yr</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>Services each way × 2 × operating days × route length</t>
-        </is>
-      </c>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Prompt.md</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Operating cost per train-km</t>
-        </is>
-      </c>
-      <c r="B16" s="8" t="n"/>
+          <t>Cost of capital — case 1</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="n">
+        <v>0.05</v>
+      </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MXN / train-km</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>All-in: crew, energy, maintenance, track access, overhead</t>
-        </is>
-      </c>
+          <t>% / yr</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Prompt.md</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Annual operating cost</t>
-        </is>
-      </c>
-      <c r="B17" s="9">
-        <f>IF(OR(B15="",B16=""),"",B15*B16/1000000)</f>
-        <v/>
+          <t>Cost of capital — case 2</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="n">
+        <v>0.06</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MXN million / yr</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>% / yr</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Prompt.md</t>
+        </is>
+      </c>
       <c r="E17" s="3" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>REVENUE</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="n"/>
-      <c r="C18" s="6" t="n"/>
-      <c r="D18" s="6" t="n"/>
-      <c r="E18" s="6" t="n"/>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Cost of capital — case 3</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>% / yr</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Prompt.md</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Average fare per trip</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="n"/>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>MXN</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>Blended across classes and distances actually travelled</t>
-        </is>
-      </c>
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>OPERATING</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n"/>
+      <c r="C19" s="6" t="n"/>
+      <c r="D19" s="6" t="n"/>
+      <c r="E19" s="6" t="n"/>
+      <c r="F19" s="6" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Non-fare revenue per trip</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="n"/>
+          <t>Fixed O&amp;M (tonnage-independent)</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="n"/>
       <c r="C20" t="inlineStr">
         <is>
-          <t>MXN</t>
+          <t>MXN million / yr</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>Concessions, advertising, parking; 0 is a defensible screen value</t>
+          <t>Signalling, admin, inspection, right-of-way security</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Average revenue per trip</t>
-        </is>
-      </c>
-      <c r="B21" s="9">
-        <f>IF(OR(B19="",B20=""),"",B19+B20)</f>
-        <v/>
-      </c>
+          <t>Variable O&amp;M per gross ton-km</t>
+        </is>
+      </c>
+      <c r="B21" s="12" t="n"/>
       <c r="C21" t="inlineStr">
         <is>
-          <t>MXN</t>
+          <t>MXN / gross ton-km</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
-      <c r="E21" s="3" t="inlineStr"/>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Track wear. This is what makes O&amp;M depend on the tonnage being solved for</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>DEMAND</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="n"/>
-      <c r="C22" s="6" t="n"/>
-      <c r="D22" s="6" t="n"/>
-      <c r="E22" s="6" t="n"/>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Tare factor (gross / net tonnage)</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="n"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>ratio</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Wagon tare + locomotive. Gross ton-km = net tons x (1 + tare) x km</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Corridor travel, all modes</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="n"/>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>trips / yr</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>Observed bus + air + private vehicle. NOT derived from population — risk R-03</t>
-        </is>
-      </c>
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>REVENUE</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n"/>
+      <c r="C23" s="6" t="n"/>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="6" t="n"/>
+      <c r="F23" s="6" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Assumed rail mode capture</t>
-        </is>
-      </c>
-      <c r="B24" s="10" t="n"/>
+          <t>Contribution margin per net ton-km</t>
+        </is>
+      </c>
+      <c r="B24" s="13" t="n"/>
       <c r="C24" t="inlineStr">
         <is>
-          <t>% of corridor travel</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
+          <t>MXN / net ton-km</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>[NOT OBTAINED]</t>
+        </is>
+      </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>The assumption most likely to be wrong — risk R-04. State it, test it on 'Sensitivity'</t>
+          <t>ARTF Anuario unreachable (bot challenge); commodity-level margin is commercially confidential. SWEPT on 'Breakeven' rather than assumed here</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Projected annual ridership</t>
-        </is>
-      </c>
-      <c r="B25" s="11">
-        <f>IF(OR(B23="",B24=""),"",B23*B24)</f>
-        <v/>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>trips / yr</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" s="3" t="inlineStr"/>
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>CONVENTIONS AND CONVERSION</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n"/>
+      <c r="C25" s="6" t="n"/>
+      <c r="D25" s="6" t="n"/>
+      <c r="E25" s="6" t="n"/>
+      <c r="F25" s="6" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>CONVENTIONS</t>
-        </is>
-      </c>
-      <c r="B26" s="6" t="n"/>
-      <c r="C26" s="6" t="n"/>
-      <c r="D26" s="6" t="n"/>
-      <c r="E26" s="6" t="n"/>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>MXN / USD rate</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="n"/>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>MXN per USD</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>State the rate AND its date. Required before any USD benchmark is used</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Base year</t>
-        </is>
-      </c>
-      <c r="B27" s="12" t="n"/>
+          <t>FX rate date</t>
+        </is>
+      </c>
+      <c r="B27" s="14" t="n"/>
       <c r="C27" t="inlineStr">
         <is>
-          <t>yyyy</t>
+          <t>date</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>All money figures are real terms in this year</t>
-        </is>
-      </c>
+      <c r="E27" s="3" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Currency</t>
-        </is>
-      </c>
-      <c r="B28" s="12" t="n"/>
-      <c r="C28" t="inlineStr"/>
+          <t>Deflation base year (INEGI INPC)</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="n"/>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>yyyy</t>
+        </is>
+      </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>MXN throughout; convert at a stated rate and record it</t>
+          <t>All money figures real in this year. Never mix nominal across years</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>FX rate used, if any</t>
-        </is>
-      </c>
-      <c r="B29" s="8" t="n"/>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>MXN / USD</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" s="3" t="inlineStr"/>
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>ROAD COMPARISON</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+      <c r="E29" s="6" t="n"/>
+      <c r="F29" s="6" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Payload per loaded articulated truck</t>
+        </is>
+      </c>
+      <c r="B30" s="15" t="n"/>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>tonnes</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Bridge from vehicle counts to tonnage. This is an ASSUMPTION — show sensitivity</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Empty-running share</t>
+        </is>
+      </c>
+      <c r="B31" s="16" t="n"/>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>fraction</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Prompt.md: ~30–50%</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>Raw truck counts are NOT loaded tonnage</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Observed articulated veh/day at corridor terminus</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="n">
+        <v>500</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>veh/day, both dirs</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>sct-2025-datosviales-oaxaca</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>SR-2 bound: endpoint flow N of Oaxaca City. See working/sr2-evaluation.md</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1174,330 +1295,173 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="72" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Breakeven</t>
+          <t>Capital cost band</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Blank output means an input it depends on has not been established. That is the correct display.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Output</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>Basis</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>Notes</t>
+          <t>Track condition is unknown since 2003 and cannot be resolved from a desk, so capital is bounded by scenario rather than assumed to a base case.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>ANNUAL COST</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n"/>
-      <c r="C4" s="6" t="n"/>
-      <c r="D4" s="6" t="n"/>
-      <c r="E4" s="6" t="n"/>
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Cost per km (MXN m)</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Linework (MXN m)</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Structures low (MXN m)</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Structures high (MXN m)</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL low (MXN m)</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL high (MXN m)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Annual operating cost</t>
-        </is>
-      </c>
-      <c r="B5" s="9">
-        <f>Assumptions!B17</f>
-        <v/>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>MXN million / yr</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Assumptions B17</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr"/>
+          <t>Light rehabilitation</t>
+        </is>
+      </c>
+      <c r="B5" s="8">
+        <f>Inputs!B7</f>
+        <v/>
+      </c>
+      <c r="C5" s="17">
+        <f>IF(OR(B5="",Inputs!$B$5=""),"",B5*Inputs!$B$5)</f>
+        <v/>
+      </c>
+      <c r="D5" s="17">
+        <f>Inputs!$B$12</f>
+        <v/>
+      </c>
+      <c r="E5" s="17">
+        <f>Inputs!$B$13</f>
+        <v/>
+      </c>
+      <c r="F5" s="17">
+        <f>IF(OR(C5="",D5=""),"",C5+D5)</f>
+        <v/>
+      </c>
+      <c r="G5" s="17">
+        <f>IF(OR(C5="",E5=""),"",C5+E5)</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Annualised capital charge</t>
-        </is>
-      </c>
-      <c r="B6" s="9">
-        <f>Assumptions!B11</f>
-        <v/>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>MXN million / yr</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Assumptions B11</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr"/>
+          <t>Heavy rehabilitation</t>
+        </is>
+      </c>
+      <c r="B6" s="8">
+        <f>Inputs!B8</f>
+        <v/>
+      </c>
+      <c r="C6" s="17">
+        <f>IF(OR(B6="",Inputs!$B$5=""),"",B6*Inputs!$B$5)</f>
+        <v/>
+      </c>
+      <c r="D6" s="17">
+        <f>Inputs!$B$12</f>
+        <v/>
+      </c>
+      <c r="E6" s="17">
+        <f>Inputs!$B$13</f>
+        <v/>
+      </c>
+      <c r="F6" s="17">
+        <f>IF(OR(C6="",D6=""),"",C6+D6)</f>
+        <v/>
+      </c>
+      <c r="G6" s="17">
+        <f>IF(OR(C6="",E6=""),"",C6+E6)</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total annual cost</t>
-        </is>
-      </c>
-      <c r="B7" s="9">
-        <f>IF(OR(B5="",B6=""),"",B5+B6)</f>
-        <v/>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>MXN million / yr</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" s="3" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>BREAKEVEN RIDERSHIP</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="n"/>
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="6" t="n"/>
-      <c r="E8" s="6" t="n"/>
+          <t>Substantial reconstruction</t>
+        </is>
+      </c>
+      <c r="B7" s="8">
+        <f>Inputs!B9</f>
+        <v/>
+      </c>
+      <c r="C7" s="17">
+        <f>IF(OR(B7="",Inputs!$B$5=""),"",B7*Inputs!$B$5)</f>
+        <v/>
+      </c>
+      <c r="D7" s="17">
+        <f>Inputs!$B$12</f>
+        <v/>
+      </c>
+      <c r="E7" s="17">
+        <f>Inputs!$B$13</f>
+        <v/>
+      </c>
+      <c r="F7" s="17">
+        <f>IF(OR(C7="",D7=""),"",C7+D7)</f>
+        <v/>
+      </c>
+      <c r="G7" s="17">
+        <f>IF(OR(C7="",E7=""),"",C7+E7)</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Average revenue per trip</t>
-        </is>
-      </c>
-      <c r="B9" s="9">
-        <f>Assumptions!B21</f>
-        <v/>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>MXN</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Assumptions B21</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr"/>
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Structures (bridges, drainage, slope stabilisation) are shown as their own range, not folded into a contingency percentage — they are the dominant uncertainty on this alignment and no public structure inventory is expected.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Breakeven — operating cost only</t>
-        </is>
-      </c>
-      <c r="B10" s="11">
-        <f>IF(OR(B5="",B9="",B9=0),"",B5*1000000/B9)</f>
-        <v/>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>trips / yr</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>The screening figure: can the line cover the cost of running it?</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Breakeven — operating + capital</t>
-        </is>
-      </c>
-      <c r="B11" s="11">
-        <f>IF(OR(B7="",B9="",B9=0),"",B7*1000000/B9)</f>
-        <v/>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>trips / yr</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>Shown separately: funding model is unknown at screen stage</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>AGAINST ACTUAL CORRIDOR TRAVEL</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="n"/>
-      <c r="C12" s="6" t="n"/>
-      <c r="D12" s="6" t="n"/>
-      <c r="E12" s="6" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Corridor travel, all modes</t>
-        </is>
-      </c>
-      <c r="B13" s="11">
-        <f>Assumptions!B23</f>
-        <v/>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>trips / yr</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Assumptions B23</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Operating breakeven as share of all corridor travel</t>
-        </is>
-      </c>
-      <c r="B14" s="13">
-        <f>IF(OR(B10="",B13="",B13=0),"",B10/B13)</f>
-        <v/>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>Above 100% means SR-2 triggers: unbuildable demand case</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Projected annual ridership</t>
-        </is>
-      </c>
-      <c r="B15" s="11">
-        <f>Assumptions!B25</f>
-        <v/>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>trips / yr</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Assumptions B25</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Margin over operating breakeven</t>
-        </is>
-      </c>
-      <c r="B16" s="11">
-        <f>IF(OR(B15="",B10=""),"",B15-B10)</f>
-        <v/>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>trips / yr</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>Negative means the assumed capture rate does not cover operating cost</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>STOP RULE SR-2</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="n"/>
-      <c r="C17" s="6" t="n"/>
-      <c r="D17" s="6" t="n"/>
-      <c r="E17" s="6" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Demand floor test</t>
-        </is>
-      </c>
-      <c r="B18" s="14">
-        <f>IF(OR(B10="",B13=""),"pending inputs",IF(B10&gt;B13,"SR-2 TRIGGERED — breakeven exceeds all corridor travel at 100% capture","SR-2 not triggered"))</f>
-        <v/>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>Record the result in deliverables/feasibility_screen.md §2</t>
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>The Cañada de Cuicatlán sits where Sierra Madre Oriental and Sierra Madre del Sur folding converge; documented rainy-season suspension implies scour and slope exposure at water crossings.</t>
         </is>
       </c>
     </row>
@@ -1512,230 +1476,1116 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Sensitivity — fare</t>
+          <t>Breakeven tonnage back-solve</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Breakeven is close to linear in fare, so this grid mostly guards against a conclusion resting on one optimistic fare assumption.</t>
+          <t>T = (AnnualCapital + FixedOM) / ( L × ( margin − varOM × (1+tare) ) ).  Closed form: revenue and variable O&amp;M are both linear in tonnage, so the O&amp;M circularity resolves algebraically rather than by iteration.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Read row 8 first: if breakeven exceeds 100% of corridor travel anywhere in the plausible fare range, the demand case is fragile.</t>
+      <c r="A3" s="18" t="inlineStr">
+        <is>
+          <t>If margin − varOM×(1+tare) ≤ 0 the line loses money on every incremental tonne and NO tonnage breaks even. The sheet says so rather than returning a number.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>Fare scenario</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>-20%</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>-10%</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>base</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>+10%</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>+20%</t>
-        </is>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Net contribution per net ton-km after track wear</t>
+        </is>
+      </c>
+      <c r="B5" s="19">
+        <f>IF(OR(Inputs!B24="",Inputs!B21="",Inputs!B22=""),"",Inputs!B24-Inputs!B21*(1+Inputs!B22))</f>
+        <v/>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>MXN / net ton-km</t>
+        </is>
+      </c>
+      <c r="D5" s="2">
+        <f>IF(B5="","pending margin + O&amp;M inputs",IF(B5&lt;=0,"NO TONNAGE BREAKS EVEN — track wear exceeds margin","positive contribution"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Capital scenario</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Capital (MXN m)</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Cost of capital</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Annualised capital (MXN m/yr)</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Fixed O&amp;M (MXN m/yr)</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>BREAKEVEN tonnage (net t/yr)</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>Loaded truckloads/day each way</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Light rehab (low structures)</t>
+        </is>
+      </c>
+      <c r="B8" s="17">
+        <f>Capital!F5</f>
+        <v/>
+      </c>
+      <c r="C8" s="20">
+        <f>Inputs!$B$16</f>
+        <v/>
+      </c>
+      <c r="D8" s="17">
+        <f>IF(OR(B8="",C8="",Inputs!$B$15=""),"",-PMT(C8,Inputs!$B$15,B8))</f>
+        <v/>
+      </c>
+      <c r="E8" s="17">
+        <f>Inputs!$B$20</f>
+        <v/>
+      </c>
+      <c r="F8" s="21">
+        <f>IF(OR(D8="",E8="",$B$5="",$B$5&lt;=0,Inputs!$B$5=""),"",(D8+E8)*1000000/(Inputs!$B$5*$B$5))</f>
+        <v/>
+      </c>
+      <c r="G8" s="21">
+        <f>IF(OR(F8="",Inputs!$B$30="",Inputs!$B$30=0),"",F8/(Inputs!$B$30*365*2))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Light rehab (low structures)</t>
+        </is>
+      </c>
+      <c r="B9" s="17">
+        <f>Capital!F5</f>
+        <v/>
+      </c>
+      <c r="C9" s="20">
+        <f>Inputs!$B$17</f>
+        <v/>
+      </c>
+      <c r="D9" s="17">
+        <f>IF(OR(B9="",C9="",Inputs!$B$15=""),"",-PMT(C9,Inputs!$B$15,B9))</f>
+        <v/>
+      </c>
+      <c r="E9" s="17">
+        <f>Inputs!$B$20</f>
+        <v/>
+      </c>
+      <c r="F9" s="21">
+        <f>IF(OR(D9="",E9="",$B$5="",$B$5&lt;=0,Inputs!$B$5=""),"",(D9+E9)*1000000/(Inputs!$B$5*$B$5))</f>
+        <v/>
+      </c>
+      <c r="G9" s="21">
+        <f>IF(OR(F9="",Inputs!$B$30="",Inputs!$B$30=0),"",F9/(Inputs!$B$30*365*2))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Light rehab (low structures)</t>
+        </is>
+      </c>
+      <c r="B10" s="17">
+        <f>Capital!F5</f>
+        <v/>
+      </c>
+      <c r="C10" s="20">
+        <f>Inputs!$B$18</f>
+        <v/>
+      </c>
+      <c r="D10" s="17">
+        <f>IF(OR(B10="",C10="",Inputs!$B$15=""),"",-PMT(C10,Inputs!$B$15,B10))</f>
+        <v/>
+      </c>
+      <c r="E10" s="17">
+        <f>Inputs!$B$20</f>
+        <v/>
+      </c>
+      <c r="F10" s="21">
+        <f>IF(OR(D10="",E10="",$B$5="",$B$5&lt;=0,Inputs!$B$5=""),"",(D10+E10)*1000000/(Inputs!$B$5*$B$5))</f>
+        <v/>
+      </c>
+      <c r="G10" s="21">
+        <f>IF(OR(F10="",Inputs!$B$30="",Inputs!$B$30=0),"",F10/(Inputs!$B$30*365*2))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Light rehab (high structures)</t>
+        </is>
+      </c>
+      <c r="B11" s="17">
+        <f>Capital!G5</f>
+        <v/>
+      </c>
+      <c r="C11" s="20">
+        <f>Inputs!$B$16</f>
+        <v/>
+      </c>
+      <c r="D11" s="17">
+        <f>IF(OR(B11="",C11="",Inputs!$B$15=""),"",-PMT(C11,Inputs!$B$15,B11))</f>
+        <v/>
+      </c>
+      <c r="E11" s="17">
+        <f>Inputs!$B$20</f>
+        <v/>
+      </c>
+      <c r="F11" s="21">
+        <f>IF(OR(D11="",E11="",$B$5="",$B$5&lt;=0,Inputs!$B$5=""),"",(D11+E11)*1000000/(Inputs!$B$5*$B$5))</f>
+        <v/>
+      </c>
+      <c r="G11" s="21">
+        <f>IF(OR(F11="",Inputs!$B$30="",Inputs!$B$30=0),"",F11/(Inputs!$B$30*365*2))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Light rehab (high structures)</t>
+        </is>
+      </c>
+      <c r="B12" s="17">
+        <f>Capital!G5</f>
+        <v/>
+      </c>
+      <c r="C12" s="20">
+        <f>Inputs!$B$17</f>
+        <v/>
+      </c>
+      <c r="D12" s="17">
+        <f>IF(OR(B12="",C12="",Inputs!$B$15=""),"",-PMT(C12,Inputs!$B$15,B12))</f>
+        <v/>
+      </c>
+      <c r="E12" s="17">
+        <f>Inputs!$B$20</f>
+        <v/>
+      </c>
+      <c r="F12" s="21">
+        <f>IF(OR(D12="",E12="",$B$5="",$B$5&lt;=0,Inputs!$B$5=""),"",(D12+E12)*1000000/(Inputs!$B$5*$B$5))</f>
+        <v/>
+      </c>
+      <c r="G12" s="21">
+        <f>IF(OR(F12="",Inputs!$B$30="",Inputs!$B$30=0),"",F12/(Inputs!$B$30*365*2))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Light rehab (high structures)</t>
+        </is>
+      </c>
+      <c r="B13" s="17">
+        <f>Capital!G5</f>
+        <v/>
+      </c>
+      <c r="C13" s="20">
+        <f>Inputs!$B$18</f>
+        <v/>
+      </c>
+      <c r="D13" s="17">
+        <f>IF(OR(B13="",C13="",Inputs!$B$15=""),"",-PMT(C13,Inputs!$B$15,B13))</f>
+        <v/>
+      </c>
+      <c r="E13" s="17">
+        <f>Inputs!$B$20</f>
+        <v/>
+      </c>
+      <c r="F13" s="21">
+        <f>IF(OR(D13="",E13="",$B$5="",$B$5&lt;=0,Inputs!$B$5=""),"",(D13+E13)*1000000/(Inputs!$B$5*$B$5))</f>
+        <v/>
+      </c>
+      <c r="G13" s="21">
+        <f>IF(OR(F13="",Inputs!$B$30="",Inputs!$B$30=0),"",F13/(Inputs!$B$30*365*2))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Heavy rehab (low structures)</t>
+        </is>
+      </c>
+      <c r="B14" s="17">
+        <f>Capital!F6</f>
+        <v/>
+      </c>
+      <c r="C14" s="20">
+        <f>Inputs!$B$16</f>
+        <v/>
+      </c>
+      <c r="D14" s="17">
+        <f>IF(OR(B14="",C14="",Inputs!$B$15=""),"",-PMT(C14,Inputs!$B$15,B14))</f>
+        <v/>
+      </c>
+      <c r="E14" s="17">
+        <f>Inputs!$B$20</f>
+        <v/>
+      </c>
+      <c r="F14" s="21">
+        <f>IF(OR(D14="",E14="",$B$5="",$B$5&lt;=0,Inputs!$B$5=""),"",(D14+E14)*1000000/(Inputs!$B$5*$B$5))</f>
+        <v/>
+      </c>
+      <c r="G14" s="21">
+        <f>IF(OR(F14="",Inputs!$B$30="",Inputs!$B$30=0),"",F14/(Inputs!$B$30*365*2))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Heavy rehab (low structures)</t>
+        </is>
+      </c>
+      <c r="B15" s="17">
+        <f>Capital!F6</f>
+        <v/>
+      </c>
+      <c r="C15" s="20">
+        <f>Inputs!$B$17</f>
+        <v/>
+      </c>
+      <c r="D15" s="17">
+        <f>IF(OR(B15="",C15="",Inputs!$B$15=""),"",-PMT(C15,Inputs!$B$15,B15))</f>
+        <v/>
+      </c>
+      <c r="E15" s="17">
+        <f>Inputs!$B$20</f>
+        <v/>
+      </c>
+      <c r="F15" s="21">
+        <f>IF(OR(D15="",E15="",$B$5="",$B$5&lt;=0,Inputs!$B$5=""),"",(D15+E15)*1000000/(Inputs!$B$5*$B$5))</f>
+        <v/>
+      </c>
+      <c r="G15" s="21">
+        <f>IF(OR(F15="",Inputs!$B$30="",Inputs!$B$30=0),"",F15/(Inputs!$B$30*365*2))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Heavy rehab (low structures)</t>
+        </is>
+      </c>
+      <c r="B16" s="17">
+        <f>Capital!F6</f>
+        <v/>
+      </c>
+      <c r="C16" s="20">
+        <f>Inputs!$B$18</f>
+        <v/>
+      </c>
+      <c r="D16" s="17">
+        <f>IF(OR(B16="",C16="",Inputs!$B$15=""),"",-PMT(C16,Inputs!$B$15,B16))</f>
+        <v/>
+      </c>
+      <c r="E16" s="17">
+        <f>Inputs!$B$20</f>
+        <v/>
+      </c>
+      <c r="F16" s="21">
+        <f>IF(OR(D16="",E16="",$B$5="",$B$5&lt;=0,Inputs!$B$5=""),"",(D16+E16)*1000000/(Inputs!$B$5*$B$5))</f>
+        <v/>
+      </c>
+      <c r="G16" s="21">
+        <f>IF(OR(F16="",Inputs!$B$30="",Inputs!$B$30=0),"",F16/(Inputs!$B$30*365*2))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Heavy rehab (high structures)</t>
+        </is>
+      </c>
+      <c r="B17" s="17">
+        <f>Capital!G6</f>
+        <v/>
+      </c>
+      <c r="C17" s="20">
+        <f>Inputs!$B$16</f>
+        <v/>
+      </c>
+      <c r="D17" s="17">
+        <f>IF(OR(B17="",C17="",Inputs!$B$15=""),"",-PMT(C17,Inputs!$B$15,B17))</f>
+        <v/>
+      </c>
+      <c r="E17" s="17">
+        <f>Inputs!$B$20</f>
+        <v/>
+      </c>
+      <c r="F17" s="21">
+        <f>IF(OR(D17="",E17="",$B$5="",$B$5&lt;=0,Inputs!$B$5=""),"",(D17+E17)*1000000/(Inputs!$B$5*$B$5))</f>
+        <v/>
+      </c>
+      <c r="G17" s="21">
+        <f>IF(OR(F17="",Inputs!$B$30="",Inputs!$B$30=0),"",F17/(Inputs!$B$30*365*2))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Heavy rehab (high structures)</t>
+        </is>
+      </c>
+      <c r="B18" s="17">
+        <f>Capital!G6</f>
+        <v/>
+      </c>
+      <c r="C18" s="20">
+        <f>Inputs!$B$17</f>
+        <v/>
+      </c>
+      <c r="D18" s="17">
+        <f>IF(OR(B18="",C18="",Inputs!$B$15=""),"",-PMT(C18,Inputs!$B$15,B18))</f>
+        <v/>
+      </c>
+      <c r="E18" s="17">
+        <f>Inputs!$B$20</f>
+        <v/>
+      </c>
+      <c r="F18" s="21">
+        <f>IF(OR(D18="",E18="",$B$5="",$B$5&lt;=0,Inputs!$B$5=""),"",(D18+E18)*1000000/(Inputs!$B$5*$B$5))</f>
+        <v/>
+      </c>
+      <c r="G18" s="21">
+        <f>IF(OR(F18="",Inputs!$B$30="",Inputs!$B$30=0),"",F18/(Inputs!$B$30*365*2))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Heavy rehab (high structures)</t>
+        </is>
+      </c>
+      <c r="B19" s="17">
+        <f>Capital!G6</f>
+        <v/>
+      </c>
+      <c r="C19" s="20">
+        <f>Inputs!$B$18</f>
+        <v/>
+      </c>
+      <c r="D19" s="17">
+        <f>IF(OR(B19="",C19="",Inputs!$B$15=""),"",-PMT(C19,Inputs!$B$15,B19))</f>
+        <v/>
+      </c>
+      <c r="E19" s="17">
+        <f>Inputs!$B$20</f>
+        <v/>
+      </c>
+      <c r="F19" s="21">
+        <f>IF(OR(D19="",E19="",$B$5="",$B$5&lt;=0,Inputs!$B$5=""),"",(D19+E19)*1000000/(Inputs!$B$5*$B$5))</f>
+        <v/>
+      </c>
+      <c r="G19" s="21">
+        <f>IF(OR(F19="",Inputs!$B$30="",Inputs!$B$30=0),"",F19/(Inputs!$B$30*365*2))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Substantial recon (low struct.)</t>
+        </is>
+      </c>
+      <c r="B20" s="17">
+        <f>Capital!F7</f>
+        <v/>
+      </c>
+      <c r="C20" s="20">
+        <f>Inputs!$B$16</f>
+        <v/>
+      </c>
+      <c r="D20" s="17">
+        <f>IF(OR(B20="",C20="",Inputs!$B$15=""),"",-PMT(C20,Inputs!$B$15,B20))</f>
+        <v/>
+      </c>
+      <c r="E20" s="17">
+        <f>Inputs!$B$20</f>
+        <v/>
+      </c>
+      <c r="F20" s="21">
+        <f>IF(OR(D20="",E20="",$B$5="",$B$5&lt;=0,Inputs!$B$5=""),"",(D20+E20)*1000000/(Inputs!$B$5*$B$5))</f>
+        <v/>
+      </c>
+      <c r="G20" s="21">
+        <f>IF(OR(F20="",Inputs!$B$30="",Inputs!$B$30=0),"",F20/(Inputs!$B$30*365*2))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Substantial recon (low struct.)</t>
+        </is>
+      </c>
+      <c r="B21" s="17">
+        <f>Capital!F7</f>
+        <v/>
+      </c>
+      <c r="C21" s="20">
+        <f>Inputs!$B$17</f>
+        <v/>
+      </c>
+      <c r="D21" s="17">
+        <f>IF(OR(B21="",C21="",Inputs!$B$15=""),"",-PMT(C21,Inputs!$B$15,B21))</f>
+        <v/>
+      </c>
+      <c r="E21" s="17">
+        <f>Inputs!$B$20</f>
+        <v/>
+      </c>
+      <c r="F21" s="21">
+        <f>IF(OR(D21="",E21="",$B$5="",$B$5&lt;=0,Inputs!$B$5=""),"",(D21+E21)*1000000/(Inputs!$B$5*$B$5))</f>
+        <v/>
+      </c>
+      <c r="G21" s="21">
+        <f>IF(OR(F21="",Inputs!$B$30="",Inputs!$B$30=0),"",F21/(Inputs!$B$30*365*2))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Substantial recon (low struct.)</t>
+        </is>
+      </c>
+      <c r="B22" s="17">
+        <f>Capital!F7</f>
+        <v/>
+      </c>
+      <c r="C22" s="20">
+        <f>Inputs!$B$18</f>
+        <v/>
+      </c>
+      <c r="D22" s="17">
+        <f>IF(OR(B22="",C22="",Inputs!$B$15=""),"",-PMT(C22,Inputs!$B$15,B22))</f>
+        <v/>
+      </c>
+      <c r="E22" s="17">
+        <f>Inputs!$B$20</f>
+        <v/>
+      </c>
+      <c r="F22" s="21">
+        <f>IF(OR(D22="",E22="",$B$5="",$B$5&lt;=0,Inputs!$B$5=""),"",(D22+E22)*1000000/(Inputs!$B$5*$B$5))</f>
+        <v/>
+      </c>
+      <c r="G22" s="21">
+        <f>IF(OR(F22="",Inputs!$B$30="",Inputs!$B$30=0),"",F22/(Inputs!$B$30*365*2))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Substantial recon (high struct.)</t>
+        </is>
+      </c>
+      <c r="B23" s="17">
+        <f>Capital!G7</f>
+        <v/>
+      </c>
+      <c r="C23" s="20">
+        <f>Inputs!$B$16</f>
+        <v/>
+      </c>
+      <c r="D23" s="17">
+        <f>IF(OR(B23="",C23="",Inputs!$B$15=""),"",-PMT(C23,Inputs!$B$15,B23))</f>
+        <v/>
+      </c>
+      <c r="E23" s="17">
+        <f>Inputs!$B$20</f>
+        <v/>
+      </c>
+      <c r="F23" s="21">
+        <f>IF(OR(D23="",E23="",$B$5="",$B$5&lt;=0,Inputs!$B$5=""),"",(D23+E23)*1000000/(Inputs!$B$5*$B$5))</f>
+        <v/>
+      </c>
+      <c r="G23" s="21">
+        <f>IF(OR(F23="",Inputs!$B$30="",Inputs!$B$30=0),"",F23/(Inputs!$B$30*365*2))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Substantial recon (high struct.)</t>
+        </is>
+      </c>
+      <c r="B24" s="17">
+        <f>Capital!G7</f>
+        <v/>
+      </c>
+      <c r="C24" s="20">
+        <f>Inputs!$B$17</f>
+        <v/>
+      </c>
+      <c r="D24" s="17">
+        <f>IF(OR(B24="",C24="",Inputs!$B$15=""),"",-PMT(C24,Inputs!$B$15,B24))</f>
+        <v/>
+      </c>
+      <c r="E24" s="17">
+        <f>Inputs!$B$20</f>
+        <v/>
+      </c>
+      <c r="F24" s="21">
+        <f>IF(OR(D24="",E24="",$B$5="",$B$5&lt;=0,Inputs!$B$5=""),"",(D24+E24)*1000000/(Inputs!$B$5*$B$5))</f>
+        <v/>
+      </c>
+      <c r="G24" s="21">
+        <f>IF(OR(F24="",Inputs!$B$30="",Inputs!$B$30=0),"",F24/(Inputs!$B$30*365*2))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Substantial recon (high struct.)</t>
+        </is>
+      </c>
+      <c r="B25" s="17">
+        <f>Capital!G7</f>
+        <v/>
+      </c>
+      <c r="C25" s="20">
+        <f>Inputs!$B$18</f>
+        <v/>
+      </c>
+      <c r="D25" s="17">
+        <f>IF(OR(B25="",C25="",Inputs!$B$15=""),"",-PMT(C25,Inputs!$B$15,B25))</f>
+        <v/>
+      </c>
+      <c r="E25" s="17">
+        <f>Inputs!$B$20</f>
+        <v/>
+      </c>
+      <c r="F25" s="21">
+        <f>IF(OR(D25="",E25="",$B$5="",$B$5&lt;=0,Inputs!$B$5=""),"",(D25+E25)*1000000/(Inputs!$B$5*$B$5))</f>
+        <v/>
+      </c>
+      <c r="G25" s="21">
+        <f>IF(OR(F25="",Inputs!$B$30="",Inputs!$B$30=0),"",F25/(Inputs!$B$30*365*2))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>STOP RULE 3 — does the answer flip across track-condition scenarios?</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Compare the breakeven range above against divertible tonnage on 'Compare'. If the project clears under light rehabilitation and fails under substantial reconstruction, the correct output is INDETERMINATE pending field reconnaissance — not a base case with a verdict attached. Report the scenario at which it flips: that is the single most decision-relevant number in the study.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Commodity segregation and mode-diversion assumptions</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>The decisive analytical step. Diversion rates are ASSUMPTIONS and the answer is highly sensitive to them — each needs its own cited source before use.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Commodity class</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Rail-divertible?</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Corridor tonnage (t/yr)</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Diversion rate</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Divertible tonnage (t/yr)</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Source for diversion rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Cement</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C5" s="14" t="n"/>
+      <c r="D5" s="11" t="n"/>
+      <c r="E5" s="21">
+        <f>IF(OR(C5="",D5=""),"",C5*D5)</f>
+        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Average fare per trip (MXN)</t>
-        </is>
-      </c>
-      <c r="B6" s="9">
-        <f>IF(Assumptions!$B$19="","",Assumptions!$B$19*0.8)</f>
-        <v/>
-      </c>
-      <c r="C6" s="9">
-        <f>IF(Assumptions!$B$19="","",Assumptions!$B$19*0.9)</f>
-        <v/>
-      </c>
-      <c r="D6" s="9">
-        <f>IF(Assumptions!$B$19="","",Assumptions!$B$19*1.0)</f>
-        <v/>
-      </c>
-      <c r="E6" s="9">
-        <f>IF(Assumptions!$B$19="","",Assumptions!$B$19*1.1)</f>
-        <v/>
-      </c>
-      <c r="F6" s="9">
-        <f>IF(Assumptions!$B$19="","",Assumptions!$B$19*1.2)</f>
+          <t>Aggregate</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="n"/>
+      <c r="D6" s="11" t="n"/>
+      <c r="E6" s="21">
+        <f>IF(OR(C6="",D6=""),"",C6*D6)</f>
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Revenue per trip incl. non-fare (MXN)</t>
-        </is>
-      </c>
-      <c r="B7" s="9">
-        <f>IF(OR(B6="",Assumptions!$B$20=""),"",B6+Assumptions!$B$20)</f>
-        <v/>
-      </c>
-      <c r="C7" s="9">
-        <f>IF(OR(C6="",Assumptions!$B$20=""),"",C6+Assumptions!$B$20)</f>
-        <v/>
-      </c>
-      <c r="D7" s="9">
-        <f>IF(OR(D6="",Assumptions!$B$20=""),"",D6+Assumptions!$B$20)</f>
-        <v/>
-      </c>
-      <c r="E7" s="9">
-        <f>IF(OR(E6="",Assumptions!$B$20=""),"",E6+Assumptions!$B$20)</f>
-        <v/>
-      </c>
-      <c r="F7" s="9">
-        <f>IF(OR(F6="",Assumptions!$B$20=""),"",F6+Assumptions!$B$20)</f>
+          <t>Fertilizer</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="n"/>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="21">
+        <f>IF(OR(C7="",D7=""),"",C7*D7)</f>
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Breakeven ridership, operating (trips/yr)</t>
-        </is>
-      </c>
-      <c r="B8" s="11">
-        <f>IF(OR(B7="",B7=0,Breakeven!$B$5=""),"",Breakeven!$B$5*1000000/B7)</f>
-        <v/>
-      </c>
-      <c r="C8" s="11">
-        <f>IF(OR(C7="",C7=0,Breakeven!$B$5=""),"",Breakeven!$B$5*1000000/C7)</f>
-        <v/>
-      </c>
-      <c r="D8" s="11">
-        <f>IF(OR(D7="",D7=0,Breakeven!$B$5=""),"",Breakeven!$B$5*1000000/D7)</f>
-        <v/>
-      </c>
-      <c r="E8" s="11">
-        <f>IF(OR(E7="",E7=0,Breakeven!$B$5=""),"",Breakeven!$B$5*1000000/E7)</f>
-        <v/>
-      </c>
-      <c r="F8" s="11">
-        <f>IF(OR(F7="",F7=0,Breakeven!$B$5=""),"",Breakeven!$B$5*1000000/F7)</f>
+          <t>Grain</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="n"/>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="21">
+        <f>IF(OR(C8="",D8=""),"",C8*D8)</f>
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>As share of all corridor travel</t>
-        </is>
-      </c>
-      <c r="B9" s="13">
-        <f>IF(OR(B8="",Assumptions!$B$23="",Assumptions!$B$23=0),"",B8/Assumptions!$B$23)</f>
-        <v/>
-      </c>
-      <c r="C9" s="13">
-        <f>IF(OR(C8="",Assumptions!$B$23="",Assumptions!$B$23=0),"",C8/Assumptions!$B$23)</f>
-        <v/>
-      </c>
-      <c r="D9" s="13">
-        <f>IF(OR(D8="",Assumptions!$B$23="",Assumptions!$B$23=0),"",D8/Assumptions!$B$23)</f>
-        <v/>
-      </c>
-      <c r="E9" s="13">
-        <f>IF(OR(E8="",Assumptions!$B$23="",Assumptions!$B$23=0),"",E8/Assumptions!$B$23)</f>
-        <v/>
-      </c>
-      <c r="F9" s="13">
-        <f>IF(OR(F8="",Assumptions!$B$23="",Assumptions!$B$23=0),"",F8/Assumptions!$B$23)</f>
+          <t>Fuel</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="n"/>
+      <c r="D9" s="11" t="n"/>
+      <c r="E9" s="21">
+        <f>IF(OR(C9="",D9=""),"",C9*D9)</f>
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Margin vs projected ridership (trips/yr)</t>
-        </is>
-      </c>
-      <c r="B10" s="11">
-        <f>IF(OR(B8="",Assumptions!$B$25=""),"",Assumptions!$B$25-B8)</f>
-        <v/>
-      </c>
-      <c r="C10" s="11">
-        <f>IF(OR(C8="",Assumptions!$B$25=""),"",Assumptions!$B$25-C8)</f>
-        <v/>
-      </c>
-      <c r="D10" s="11">
-        <f>IF(OR(D8="",Assumptions!$B$25=""),"",Assumptions!$B$25-D8)</f>
-        <v/>
-      </c>
-      <c r="E10" s="11">
-        <f>IF(OR(E8="",Assumptions!$B$25=""),"",Assumptions!$B$25-E8)</f>
-        <v/>
-      </c>
-      <c r="F10" s="11">
-        <f>IF(OR(F8="",Assumptions!$B$25=""),"",Assumptions!$B$25-F8)</f>
+          <t>Steel</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="n"/>
+      <c r="D10" s="11" t="n"/>
+      <c r="E10" s="21">
+        <f>IF(OR(C10="",D10=""),"",C10*D10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Containerised manufactured</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="n"/>
+      <c r="D11" s="11" t="n"/>
+      <c r="E11" s="21">
+        <f>IF(OR(C11="",D11=""),"",C11*D11)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>TO ADD IN PHASE 2</t>
-        </is>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Refrigerated</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="C12" s="14" t="n"/>
+      <c r="D12" s="11" t="n"/>
+      <c r="E12" s="21">
+        <f>IF(OR(C12="",D12=""),"",C12*D12)</f>
+        <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>• Capture-rate sensitivity — the dominant uncertainty (risk R-04). Vary Assumptions!B24 across a range whose low end is a rail service nobody switches to.</t>
-        </is>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Time-sensitive</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="C13" s="14" t="n"/>
+      <c r="D13" s="11" t="n"/>
+      <c r="E13" s="21">
+        <f>IF(OR(C13="",D13=""),"",C13*D13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>High-value low-density agricultural</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="C14" s="14" t="n"/>
+      <c r="D14" s="11" t="n"/>
+      <c r="E14" s="21">
+        <f>IF(OR(C14="",D14=""),"",C14*D14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>TOTAL divertible</t>
+        </is>
+      </c>
+      <c r="E15" s="22">
+        <f>IF(COUNT(E5:E14)=0,"",SUM(E5:E14))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Low-diversion classes (mezcal, coffee, avocado, mango, figs) are a large share of Oaxaca's tradeable output and are exactly the goods least likely to move by rail. Segregating them is what prevents a headline tonnage figure from overstating the case.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Aforo data classifies by axle configuration only — there is NO commodity field. Commodity mix must come from production and trade data (SIAP, INEGI Censos Económicos), not from truck counts.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="58" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Compare — divertible tonnage against breakeven</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Filled once both sides exist. Ranges, not point estimates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Divertible tonnage (bottom-up, commodity)</t>
+        </is>
+      </c>
+      <c r="B5" s="21">
+        <f>Commodity!E15</f>
+        <v/>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>t / yr</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Commodity sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Breakeven tonnage — most favourable case</t>
+        </is>
+      </c>
+      <c r="B6" s="21">
+        <f>IF(COUNT(Breakeven!F8:F25)=0,"",MIN(Breakeven!F8:F25))</f>
+        <v/>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>t / yr</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Breakeven sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Breakeven tonnage — least favourable case</t>
+        </is>
+      </c>
+      <c r="B7" s="21">
+        <f>IF(COUNT(Breakeven!F8:F25)=0,"",MAX(Breakeven!F8:F25))</f>
+        <v/>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>t / yr</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Breakeven sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Ratio: divertible / breakeven (favourable)</t>
+        </is>
+      </c>
+      <c r="B8" s="23">
+        <f>IF(OR(B5="",B6="",B6=0),"",B5/B6)</f>
+        <v/>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Ratio: divertible / breakeven (unfavourable)</t>
+        </is>
+      </c>
+      <c r="B9" s="23">
+        <f>IF(OR(B5="",B7="",B7=0),"",B5/B7)</f>
+        <v/>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>VERDICT GATE</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Stop Rule 3 test</t>
+        </is>
+      </c>
+      <c r="B12" s="24">
+        <f>IF(OR(B8="",B9=""),"pending inputs",IF(AND(B8&gt;1,B9&lt;1),"INDETERMINATE — scenarios straddle breakeven; field reconnaissance required",IF(B8&lt;1,"FAILS under every capital scenario",IF(B9&gt;1,"CLEARS under every capital scenario","review"))))</f>
+        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>• Capital cost per km sensitivity — analogue transfer error is the second dominant uncertainty (risk R-02), and matters most for the operating+capital breakeven.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>• Both are deferred until real inputs exist: a sensitivity grid over invented base values reads as analysis while carrying no information.</t>
+          <t>A straddle is a real result, not a failure to decide. Per the brief, do not select a base case and present a conclusion — report the scenario at which the answer flips.</t>
         </is>
       </c>
     </row>

--- a/analysis/breakeven_model.xlsx
+++ b/analysis/breakeven_model.xlsx
@@ -12,7 +12,8 @@
     <sheet name="Capital" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Breakeven" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Commodity" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Compare" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Supportable" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Compare" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -114,7 +115,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -130,17 +131,18 @@
     <xf numFmtId="3" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="2" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -727,7 +729,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -1123,7 +1125,9 @@
           <t>Contribution margin per net ton-km</t>
         </is>
       </c>
-      <c r="B24" s="13" t="n"/>
+      <c r="B24" s="12" t="n">
+        <v>0.402</v>
+      </c>
       <c r="C24" t="inlineStr">
         <is>
           <t>MXN / net ton-km</t>
@@ -1131,12 +1135,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>[NOT OBTAINED]</t>
+          <t>artf-2024-anuario-ferroviario</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>ARTF Anuario unreachable (bot challenge); commodity-level margin is commercially confidential. SWEPT on 'Breakeven' rather than assumed here</t>
+          <t>Ferrosur EBIT/ton-km, constant 2024 MXN: $0.93 revenue (Tabla 7-8) x 43.19% operating margin (Tablas 7-3, 7.7). ARTF's cost base ALREADY includes maintenance and D&amp;A, so B21 and B20 must be 0 when using this basis or maintenance is double-counted. Swept 0.402-0.93 on 'Supportable'. See working/margin-derivation.md</t>
         </is>
       </c>
     </row>
@@ -1177,7 +1181,7 @@
           <t>FX rate date</t>
         </is>
       </c>
-      <c r="B27" s="14" t="n"/>
+      <c r="B27" s="13" t="n"/>
       <c r="C27" t="inlineStr">
         <is>
           <t>date</t>
@@ -1223,13 +1227,19 @@
           <t>Payload per loaded articulated truck</t>
         </is>
       </c>
-      <c r="B30" s="15" t="n"/>
+      <c r="B30" s="14" t="n">
+        <v>27.5</v>
+      </c>
       <c r="C30" t="inlineStr">
         <is>
           <t>tonnes</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>[ASSUMPTION] 25–30 t</t>
+        </is>
+      </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
           <t>Bridge from vehicle counts to tonnage. This is an ASSUMPTION — show sensitivity</t>
@@ -1242,7 +1252,9 @@
           <t>Empty-running share</t>
         </is>
       </c>
-      <c r="B31" s="16" t="n"/>
+      <c r="B31" s="15" t="n">
+        <v>0.4</v>
+      </c>
       <c r="C31" t="inlineStr">
         <is>
           <t>fraction</t>
@@ -1281,6 +1293,31 @@
       <c r="E32" s="3" t="inlineStr">
         <is>
           <t>SR-2 bound: endpoint flow N of Oaxaca City. See working/sr2-evaluation.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Variable O&amp;M — set 0 on the EBIT margin basis</t>
+        </is>
+      </c>
+      <c r="B33" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>MXN / gross ton-km</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>see note</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>Guard against double-counting; overrides B21 conceptually</t>
         </is>
       </c>
     </row>
@@ -1515,7 +1552,7 @@
           <t>Net contribution per net ton-km after track wear</t>
         </is>
       </c>
-      <c r="B5" s="19">
+      <c r="B5" s="16">
         <f>IF(OR(Inputs!B24="",Inputs!B21="",Inputs!B22=""),"",Inputs!B24-Inputs!B21*(1+Inputs!B22))</f>
         <v/>
       </c>
@@ -1576,7 +1613,7 @@
         <f>Capital!F5</f>
         <v/>
       </c>
-      <c r="C8" s="20">
+      <c r="C8" s="19">
         <f>Inputs!$B$16</f>
         <v/>
       </c>
@@ -1588,11 +1625,11 @@
         <f>Inputs!$B$20</f>
         <v/>
       </c>
-      <c r="F8" s="21">
+      <c r="F8" s="20">
         <f>IF(OR(D8="",E8="",$B$5="",$B$5&lt;=0,Inputs!$B$5=""),"",(D8+E8)*1000000/(Inputs!$B$5*$B$5))</f>
         <v/>
       </c>
-      <c r="G8" s="21">
+      <c r="G8" s="20">
         <f>IF(OR(F8="",Inputs!$B$30="",Inputs!$B$30=0),"",F8/(Inputs!$B$30*365*2))</f>
         <v/>
       </c>
@@ -1607,7 +1644,7 @@
         <f>Capital!F5</f>
         <v/>
       </c>
-      <c r="C9" s="20">
+      <c r="C9" s="19">
         <f>Inputs!$B$17</f>
         <v/>
       </c>
@@ -1619,11 +1656,11 @@
         <f>Inputs!$B$20</f>
         <v/>
       </c>
-      <c r="F9" s="21">
+      <c r="F9" s="20">
         <f>IF(OR(D9="",E9="",$B$5="",$B$5&lt;=0,Inputs!$B$5=""),"",(D9+E9)*1000000/(Inputs!$B$5*$B$5))</f>
         <v/>
       </c>
-      <c r="G9" s="21">
+      <c r="G9" s="20">
         <f>IF(OR(F9="",Inputs!$B$30="",Inputs!$B$30=0),"",F9/(Inputs!$B$30*365*2))</f>
         <v/>
       </c>
@@ -1638,7 +1675,7 @@
         <f>Capital!F5</f>
         <v/>
       </c>
-      <c r="C10" s="20">
+      <c r="C10" s="19">
         <f>Inputs!$B$18</f>
         <v/>
       </c>
@@ -1650,11 +1687,11 @@
         <f>Inputs!$B$20</f>
         <v/>
       </c>
-      <c r="F10" s="21">
+      <c r="F10" s="20">
         <f>IF(OR(D10="",E10="",$B$5="",$B$5&lt;=0,Inputs!$B$5=""),"",(D10+E10)*1000000/(Inputs!$B$5*$B$5))</f>
         <v/>
       </c>
-      <c r="G10" s="21">
+      <c r="G10" s="20">
         <f>IF(OR(F10="",Inputs!$B$30="",Inputs!$B$30=0),"",F10/(Inputs!$B$30*365*2))</f>
         <v/>
       </c>
@@ -1669,7 +1706,7 @@
         <f>Capital!G5</f>
         <v/>
       </c>
-      <c r="C11" s="20">
+      <c r="C11" s="19">
         <f>Inputs!$B$16</f>
         <v/>
       </c>
@@ -1681,11 +1718,11 @@
         <f>Inputs!$B$20</f>
         <v/>
       </c>
-      <c r="F11" s="21">
+      <c r="F11" s="20">
         <f>IF(OR(D11="",E11="",$B$5="",$B$5&lt;=0,Inputs!$B$5=""),"",(D11+E11)*1000000/(Inputs!$B$5*$B$5))</f>
         <v/>
       </c>
-      <c r="G11" s="21">
+      <c r="G11" s="20">
         <f>IF(OR(F11="",Inputs!$B$30="",Inputs!$B$30=0),"",F11/(Inputs!$B$30*365*2))</f>
         <v/>
       </c>
@@ -1700,7 +1737,7 @@
         <f>Capital!G5</f>
         <v/>
       </c>
-      <c r="C12" s="20">
+      <c r="C12" s="19">
         <f>Inputs!$B$17</f>
         <v/>
       </c>
@@ -1712,11 +1749,11 @@
         <f>Inputs!$B$20</f>
         <v/>
       </c>
-      <c r="F12" s="21">
+      <c r="F12" s="20">
         <f>IF(OR(D12="",E12="",$B$5="",$B$5&lt;=0,Inputs!$B$5=""),"",(D12+E12)*1000000/(Inputs!$B$5*$B$5))</f>
         <v/>
       </c>
-      <c r="G12" s="21">
+      <c r="G12" s="20">
         <f>IF(OR(F12="",Inputs!$B$30="",Inputs!$B$30=0),"",F12/(Inputs!$B$30*365*2))</f>
         <v/>
       </c>
@@ -1731,7 +1768,7 @@
         <f>Capital!G5</f>
         <v/>
       </c>
-      <c r="C13" s="20">
+      <c r="C13" s="19">
         <f>Inputs!$B$18</f>
         <v/>
       </c>
@@ -1743,11 +1780,11 @@
         <f>Inputs!$B$20</f>
         <v/>
       </c>
-      <c r="F13" s="21">
+      <c r="F13" s="20">
         <f>IF(OR(D13="",E13="",$B$5="",$B$5&lt;=0,Inputs!$B$5=""),"",(D13+E13)*1000000/(Inputs!$B$5*$B$5))</f>
         <v/>
       </c>
-      <c r="G13" s="21">
+      <c r="G13" s="20">
         <f>IF(OR(F13="",Inputs!$B$30="",Inputs!$B$30=0),"",F13/(Inputs!$B$30*365*2))</f>
         <v/>
       </c>
@@ -1762,7 +1799,7 @@
         <f>Capital!F6</f>
         <v/>
       </c>
-      <c r="C14" s="20">
+      <c r="C14" s="19">
         <f>Inputs!$B$16</f>
         <v/>
       </c>
@@ -1774,11 +1811,11 @@
         <f>Inputs!$B$20</f>
         <v/>
       </c>
-      <c r="F14" s="21">
+      <c r="F14" s="20">
         <f>IF(OR(D14="",E14="",$B$5="",$B$5&lt;=0,Inputs!$B$5=""),"",(D14+E14)*1000000/(Inputs!$B$5*$B$5))</f>
         <v/>
       </c>
-      <c r="G14" s="21">
+      <c r="G14" s="20">
         <f>IF(OR(F14="",Inputs!$B$30="",Inputs!$B$30=0),"",F14/(Inputs!$B$30*365*2))</f>
         <v/>
       </c>
@@ -1793,7 +1830,7 @@
         <f>Capital!F6</f>
         <v/>
       </c>
-      <c r="C15" s="20">
+      <c r="C15" s="19">
         <f>Inputs!$B$17</f>
         <v/>
       </c>
@@ -1805,11 +1842,11 @@
         <f>Inputs!$B$20</f>
         <v/>
       </c>
-      <c r="F15" s="21">
+      <c r="F15" s="20">
         <f>IF(OR(D15="",E15="",$B$5="",$B$5&lt;=0,Inputs!$B$5=""),"",(D15+E15)*1000000/(Inputs!$B$5*$B$5))</f>
         <v/>
       </c>
-      <c r="G15" s="21">
+      <c r="G15" s="20">
         <f>IF(OR(F15="",Inputs!$B$30="",Inputs!$B$30=0),"",F15/(Inputs!$B$30*365*2))</f>
         <v/>
       </c>
@@ -1824,7 +1861,7 @@
         <f>Capital!F6</f>
         <v/>
       </c>
-      <c r="C16" s="20">
+      <c r="C16" s="19">
         <f>Inputs!$B$18</f>
         <v/>
       </c>
@@ -1836,11 +1873,11 @@
         <f>Inputs!$B$20</f>
         <v/>
       </c>
-      <c r="F16" s="21">
+      <c r="F16" s="20">
         <f>IF(OR(D16="",E16="",$B$5="",$B$5&lt;=0,Inputs!$B$5=""),"",(D16+E16)*1000000/(Inputs!$B$5*$B$5))</f>
         <v/>
       </c>
-      <c r="G16" s="21">
+      <c r="G16" s="20">
         <f>IF(OR(F16="",Inputs!$B$30="",Inputs!$B$30=0),"",F16/(Inputs!$B$30*365*2))</f>
         <v/>
       </c>
@@ -1855,7 +1892,7 @@
         <f>Capital!G6</f>
         <v/>
       </c>
-      <c r="C17" s="20">
+      <c r="C17" s="19">
         <f>Inputs!$B$16</f>
         <v/>
       </c>
@@ -1867,11 +1904,11 @@
         <f>Inputs!$B$20</f>
         <v/>
       </c>
-      <c r="F17" s="21">
+      <c r="F17" s="20">
         <f>IF(OR(D17="",E17="",$B$5="",$B$5&lt;=0,Inputs!$B$5=""),"",(D17+E17)*1000000/(Inputs!$B$5*$B$5))</f>
         <v/>
       </c>
-      <c r="G17" s="21">
+      <c r="G17" s="20">
         <f>IF(OR(F17="",Inputs!$B$30="",Inputs!$B$30=0),"",F17/(Inputs!$B$30*365*2))</f>
         <v/>
       </c>
@@ -1886,7 +1923,7 @@
         <f>Capital!G6</f>
         <v/>
       </c>
-      <c r="C18" s="20">
+      <c r="C18" s="19">
         <f>Inputs!$B$17</f>
         <v/>
       </c>
@@ -1898,11 +1935,11 @@
         <f>Inputs!$B$20</f>
         <v/>
       </c>
-      <c r="F18" s="21">
+      <c r="F18" s="20">
         <f>IF(OR(D18="",E18="",$B$5="",$B$5&lt;=0,Inputs!$B$5=""),"",(D18+E18)*1000000/(Inputs!$B$5*$B$5))</f>
         <v/>
       </c>
-      <c r="G18" s="21">
+      <c r="G18" s="20">
         <f>IF(OR(F18="",Inputs!$B$30="",Inputs!$B$30=0),"",F18/(Inputs!$B$30*365*2))</f>
         <v/>
       </c>
@@ -1917,7 +1954,7 @@
         <f>Capital!G6</f>
         <v/>
       </c>
-      <c r="C19" s="20">
+      <c r="C19" s="19">
         <f>Inputs!$B$18</f>
         <v/>
       </c>
@@ -1929,11 +1966,11 @@
         <f>Inputs!$B$20</f>
         <v/>
       </c>
-      <c r="F19" s="21">
+      <c r="F19" s="20">
         <f>IF(OR(D19="",E19="",$B$5="",$B$5&lt;=0,Inputs!$B$5=""),"",(D19+E19)*1000000/(Inputs!$B$5*$B$5))</f>
         <v/>
       </c>
-      <c r="G19" s="21">
+      <c r="G19" s="20">
         <f>IF(OR(F19="",Inputs!$B$30="",Inputs!$B$30=0),"",F19/(Inputs!$B$30*365*2))</f>
         <v/>
       </c>
@@ -1948,7 +1985,7 @@
         <f>Capital!F7</f>
         <v/>
       </c>
-      <c r="C20" s="20">
+      <c r="C20" s="19">
         <f>Inputs!$B$16</f>
         <v/>
       </c>
@@ -1960,11 +1997,11 @@
         <f>Inputs!$B$20</f>
         <v/>
       </c>
-      <c r="F20" s="21">
+      <c r="F20" s="20">
         <f>IF(OR(D20="",E20="",$B$5="",$B$5&lt;=0,Inputs!$B$5=""),"",(D20+E20)*1000000/(Inputs!$B$5*$B$5))</f>
         <v/>
       </c>
-      <c r="G20" s="21">
+      <c r="G20" s="20">
         <f>IF(OR(F20="",Inputs!$B$30="",Inputs!$B$30=0),"",F20/(Inputs!$B$30*365*2))</f>
         <v/>
       </c>
@@ -1979,7 +2016,7 @@
         <f>Capital!F7</f>
         <v/>
       </c>
-      <c r="C21" s="20">
+      <c r="C21" s="19">
         <f>Inputs!$B$17</f>
         <v/>
       </c>
@@ -1991,11 +2028,11 @@
         <f>Inputs!$B$20</f>
         <v/>
       </c>
-      <c r="F21" s="21">
+      <c r="F21" s="20">
         <f>IF(OR(D21="",E21="",$B$5="",$B$5&lt;=0,Inputs!$B$5=""),"",(D21+E21)*1000000/(Inputs!$B$5*$B$5))</f>
         <v/>
       </c>
-      <c r="G21" s="21">
+      <c r="G21" s="20">
         <f>IF(OR(F21="",Inputs!$B$30="",Inputs!$B$30=0),"",F21/(Inputs!$B$30*365*2))</f>
         <v/>
       </c>
@@ -2010,7 +2047,7 @@
         <f>Capital!F7</f>
         <v/>
       </c>
-      <c r="C22" s="20">
+      <c r="C22" s="19">
         <f>Inputs!$B$18</f>
         <v/>
       </c>
@@ -2022,11 +2059,11 @@
         <f>Inputs!$B$20</f>
         <v/>
       </c>
-      <c r="F22" s="21">
+      <c r="F22" s="20">
         <f>IF(OR(D22="",E22="",$B$5="",$B$5&lt;=0,Inputs!$B$5=""),"",(D22+E22)*1000000/(Inputs!$B$5*$B$5))</f>
         <v/>
       </c>
-      <c r="G22" s="21">
+      <c r="G22" s="20">
         <f>IF(OR(F22="",Inputs!$B$30="",Inputs!$B$30=0),"",F22/(Inputs!$B$30*365*2))</f>
         <v/>
       </c>
@@ -2041,7 +2078,7 @@
         <f>Capital!G7</f>
         <v/>
       </c>
-      <c r="C23" s="20">
+      <c r="C23" s="19">
         <f>Inputs!$B$16</f>
         <v/>
       </c>
@@ -2053,11 +2090,11 @@
         <f>Inputs!$B$20</f>
         <v/>
       </c>
-      <c r="F23" s="21">
+      <c r="F23" s="20">
         <f>IF(OR(D23="",E23="",$B$5="",$B$5&lt;=0,Inputs!$B$5=""),"",(D23+E23)*1000000/(Inputs!$B$5*$B$5))</f>
         <v/>
       </c>
-      <c r="G23" s="21">
+      <c r="G23" s="20">
         <f>IF(OR(F23="",Inputs!$B$30="",Inputs!$B$30=0),"",F23/(Inputs!$B$30*365*2))</f>
         <v/>
       </c>
@@ -2072,7 +2109,7 @@
         <f>Capital!G7</f>
         <v/>
       </c>
-      <c r="C24" s="20">
+      <c r="C24" s="19">
         <f>Inputs!$B$17</f>
         <v/>
       </c>
@@ -2084,11 +2121,11 @@
         <f>Inputs!$B$20</f>
         <v/>
       </c>
-      <c r="F24" s="21">
+      <c r="F24" s="20">
         <f>IF(OR(D24="",E24="",$B$5="",$B$5&lt;=0,Inputs!$B$5=""),"",(D24+E24)*1000000/(Inputs!$B$5*$B$5))</f>
         <v/>
       </c>
-      <c r="G24" s="21">
+      <c r="G24" s="20">
         <f>IF(OR(F24="",Inputs!$B$30="",Inputs!$B$30=0),"",F24/(Inputs!$B$30*365*2))</f>
         <v/>
       </c>
@@ -2103,7 +2140,7 @@
         <f>Capital!G7</f>
         <v/>
       </c>
-      <c r="C25" s="20">
+      <c r="C25" s="19">
         <f>Inputs!$B$18</f>
         <v/>
       </c>
@@ -2115,11 +2152,11 @@
         <f>Inputs!$B$20</f>
         <v/>
       </c>
-      <c r="F25" s="21">
+      <c r="F25" s="20">
         <f>IF(OR(D25="",E25="",$B$5="",$B$5&lt;=0,Inputs!$B$5=""),"",(D25+E25)*1000000/(Inputs!$B$5*$B$5))</f>
         <v/>
       </c>
-      <c r="G25" s="21">
+      <c r="G25" s="20">
         <f>IF(OR(F25="",Inputs!$B$30="",Inputs!$B$30=0),"",F25/(Inputs!$B$30*365*2))</f>
         <v/>
       </c>
@@ -2217,9 +2254,9 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="C5" s="14" t="n"/>
+      <c r="C5" s="13" t="n"/>
       <c r="D5" s="11" t="n"/>
-      <c r="E5" s="21">
+      <c r="E5" s="20">
         <f>IF(OR(C5="",D5=""),"",C5*D5)</f>
         <v/>
       </c>
@@ -2235,9 +2272,9 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="C6" s="14" t="n"/>
+      <c r="C6" s="13" t="n"/>
       <c r="D6" s="11" t="n"/>
-      <c r="E6" s="21">
+      <c r="E6" s="20">
         <f>IF(OR(C6="",D6=""),"",C6*D6)</f>
         <v/>
       </c>
@@ -2253,9 +2290,9 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="C7" s="14" t="n"/>
+      <c r="C7" s="13" t="n"/>
       <c r="D7" s="11" t="n"/>
-      <c r="E7" s="21">
+      <c r="E7" s="20">
         <f>IF(OR(C7="",D7=""),"",C7*D7)</f>
         <v/>
       </c>
@@ -2271,9 +2308,9 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="C8" s="14" t="n"/>
+      <c r="C8" s="13" t="n"/>
       <c r="D8" s="11" t="n"/>
-      <c r="E8" s="21">
+      <c r="E8" s="20">
         <f>IF(OR(C8="",D8=""),"",C8*D8)</f>
         <v/>
       </c>
@@ -2289,9 +2326,9 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="C9" s="14" t="n"/>
+      <c r="C9" s="13" t="n"/>
       <c r="D9" s="11" t="n"/>
-      <c r="E9" s="21">
+      <c r="E9" s="20">
         <f>IF(OR(C9="",D9=""),"",C9*D9)</f>
         <v/>
       </c>
@@ -2307,9 +2344,9 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="C10" s="14" t="n"/>
+      <c r="C10" s="13" t="n"/>
       <c r="D10" s="11" t="n"/>
-      <c r="E10" s="21">
+      <c r="E10" s="20">
         <f>IF(OR(C10="",D10=""),"",C10*D10)</f>
         <v/>
       </c>
@@ -2325,9 +2362,9 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="C11" s="14" t="n"/>
+      <c r="C11" s="13" t="n"/>
       <c r="D11" s="11" t="n"/>
-      <c r="E11" s="21">
+      <c r="E11" s="20">
         <f>IF(OR(C11="",D11=""),"",C11*D11)</f>
         <v/>
       </c>
@@ -2343,9 +2380,9 @@
           <t>low</t>
         </is>
       </c>
-      <c r="C12" s="14" t="n"/>
+      <c r="C12" s="13" t="n"/>
       <c r="D12" s="11" t="n"/>
-      <c r="E12" s="21">
+      <c r="E12" s="20">
         <f>IF(OR(C12="",D12=""),"",C12*D12)</f>
         <v/>
       </c>
@@ -2361,9 +2398,9 @@
           <t>low</t>
         </is>
       </c>
-      <c r="C13" s="14" t="n"/>
+      <c r="C13" s="13" t="n"/>
       <c r="D13" s="11" t="n"/>
-      <c r="E13" s="21">
+      <c r="E13" s="20">
         <f>IF(OR(C13="",D13=""),"",C13*D13)</f>
         <v/>
       </c>
@@ -2379,9 +2416,9 @@
           <t>low</t>
         </is>
       </c>
-      <c r="C14" s="14" t="n"/>
+      <c r="C14" s="13" t="n"/>
       <c r="D14" s="11" t="n"/>
-      <c r="E14" s="21">
+      <c r="E14" s="20">
         <f>IF(OR(C14="",D14=""),"",C14*D14)</f>
         <v/>
       </c>
@@ -2392,7 +2429,7 @@
           <t>TOTAL divertible</t>
         </is>
       </c>
-      <c r="E15" s="22">
+      <c r="E15" s="21">
         <f>IF(COUNT(E5:E14)=0,"",SUM(E5:E14))</f>
         <v/>
       </c>
@@ -2417,6 +2454,338 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Maximum supportable capital — the screen inverted</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>A planning-level capital cost for this alignment could not be sourced. So instead: given what the corridor demonstrably moves and what Mexican railways demonstrably earn per ton-km, how much capital could the line support? Needs no capital estimate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>CORRIDOR TONNAGE FROM OBSERVED TRAFFIC</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Articulated veh/day, both directions</t>
+        </is>
+      </c>
+      <c r="B5" s="20">
+        <f>Inputs!B32</f>
+        <v/>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>veh/day</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>sct-2025-datosviales-oaxaca (SR-2 bound)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Loaded share</t>
+        </is>
+      </c>
+      <c r="B6" s="22">
+        <f>IF(Inputs!B31="","",1-Inputs!B31)</f>
+        <v/>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>fraction</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>[ASSUMPTION] 30–50% empty</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Payload per loaded truck</t>
+        </is>
+      </c>
+      <c r="B7" s="22">
+        <f>Inputs!B30</f>
+        <v/>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>tonnes</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>[ASSUMPTION] 25–30 t</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Corridor tonnage</t>
+        </is>
+      </c>
+      <c r="B8" s="20">
+        <f>IF(OR(B5="",B6="",B7=""),"",B5*B6*B7*365)</f>
+        <v/>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>tonnes / yr</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>MAXIMUM SUPPORTABLE CAPITAL (MXN million per route-km)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Rows = share of corridor freight won by rail [ASSUMPTION]. Columns = cost of capital, 30-year life.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Diversion</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Tonnage (t/yr)</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Annual surplus (MXN m)</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>@5% MXN m/km</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>@6% MXN m/km</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>@8% MXN m/km</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="B13" s="20">
+        <f>IF($B$8="","",$B$8*A13)</f>
+        <v/>
+      </c>
+      <c r="C13" s="17">
+        <f>IF(OR(B13="",Inputs!$B$24="",Inputs!$B$5=""),"",B13*Inputs!$B$5*Inputs!$B$24/1000000)</f>
+        <v/>
+      </c>
+      <c r="D13" s="17">
+        <f>IF(OR($C13="",Inputs!$B$16="",Inputs!$B$15="",Inputs!$B$5=""),"",$C13*((1-(1+Inputs!$B$16)^-Inputs!$B$15)/Inputs!$B$16)/Inputs!$B$5)</f>
+        <v/>
+      </c>
+      <c r="E13" s="17">
+        <f>IF(OR($C13="",Inputs!$B$17="",Inputs!$B$15="",Inputs!$B$5=""),"",$C13*((1-(1+Inputs!$B$17)^-Inputs!$B$15)/Inputs!$B$17)/Inputs!$B$5)</f>
+        <v/>
+      </c>
+      <c r="F13" s="17">
+        <f>IF(OR($C13="",Inputs!$B$18="",Inputs!$B$15="",Inputs!$B$5=""),"",$C13*((1-(1+Inputs!$B$18)^-Inputs!$B$15)/Inputs!$B$18)/Inputs!$B$5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="23" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="B14" s="20">
+        <f>IF($B$8="","",$B$8*A14)</f>
+        <v/>
+      </c>
+      <c r="C14" s="17">
+        <f>IF(OR(B14="",Inputs!$B$24="",Inputs!$B$5=""),"",B14*Inputs!$B$5*Inputs!$B$24/1000000)</f>
+        <v/>
+      </c>
+      <c r="D14" s="17">
+        <f>IF(OR($C14="",Inputs!$B$16="",Inputs!$B$15="",Inputs!$B$5=""),"",$C14*((1-(1+Inputs!$B$16)^-Inputs!$B$15)/Inputs!$B$16)/Inputs!$B$5)</f>
+        <v/>
+      </c>
+      <c r="E14" s="17">
+        <f>IF(OR($C14="",Inputs!$B$17="",Inputs!$B$15="",Inputs!$B$5=""),"",$C14*((1-(1+Inputs!$B$17)^-Inputs!$B$15)/Inputs!$B$17)/Inputs!$B$5)</f>
+        <v/>
+      </c>
+      <c r="F14" s="17">
+        <f>IF(OR($C14="",Inputs!$B$18="",Inputs!$B$15="",Inputs!$B$5=""),"",$C14*((1-(1+Inputs!$B$18)^-Inputs!$B$15)/Inputs!$B$18)/Inputs!$B$5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="23" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="B15" s="20">
+        <f>IF($B$8="","",$B$8*A15)</f>
+        <v/>
+      </c>
+      <c r="C15" s="17">
+        <f>IF(OR(B15="",Inputs!$B$24="",Inputs!$B$5=""),"",B15*Inputs!$B$5*Inputs!$B$24/1000000)</f>
+        <v/>
+      </c>
+      <c r="D15" s="17">
+        <f>IF(OR($C15="",Inputs!$B$16="",Inputs!$B$15="",Inputs!$B$5=""),"",$C15*((1-(1+Inputs!$B$16)^-Inputs!$B$15)/Inputs!$B$16)/Inputs!$B$5)</f>
+        <v/>
+      </c>
+      <c r="E15" s="17">
+        <f>IF(OR($C15="",Inputs!$B$17="",Inputs!$B$15="",Inputs!$B$5=""),"",$C15*((1-(1+Inputs!$B$17)^-Inputs!$B$15)/Inputs!$B$17)/Inputs!$B$5)</f>
+        <v/>
+      </c>
+      <c r="F15" s="17">
+        <f>IF(OR($C15="",Inputs!$B$18="",Inputs!$B$15="",Inputs!$B$5=""),"",$C15*((1-(1+Inputs!$B$18)^-Inputs!$B$15)/Inputs!$B$18)/Inputs!$B$5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="23" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="B16" s="20">
+        <f>IF($B$8="","",$B$8*A16)</f>
+        <v/>
+      </c>
+      <c r="C16" s="17">
+        <f>IF(OR(B16="",Inputs!$B$24="",Inputs!$B$5=""),"",B16*Inputs!$B$5*Inputs!$B$24/1000000)</f>
+        <v/>
+      </c>
+      <c r="D16" s="17">
+        <f>IF(OR($C16="",Inputs!$B$16="",Inputs!$B$15="",Inputs!$B$5=""),"",$C16*((1-(1+Inputs!$B$16)^-Inputs!$B$15)/Inputs!$B$16)/Inputs!$B$5)</f>
+        <v/>
+      </c>
+      <c r="E16" s="17">
+        <f>IF(OR($C16="",Inputs!$B$17="",Inputs!$B$15="",Inputs!$B$5=""),"",$C16*((1-(1+Inputs!$B$17)^-Inputs!$B$15)/Inputs!$B$17)/Inputs!$B$5)</f>
+        <v/>
+      </c>
+      <c r="F16" s="17">
+        <f>IF(OR($C16="",Inputs!$B$18="",Inputs!$B$15="",Inputs!$B$5=""),"",$C16*((1-(1+Inputs!$B$18)^-Inputs!$B$15)/Inputs!$B$18)/Inputs!$B$5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>BENCHMARKS</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>UNESCAP light rehabilitation</t>
+        </is>
+      </c>
+      <c r="B20" s="22">
+        <f>IF(Inputs!B26="","",0.5*Inputs!B26)</f>
+        <v/>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>MXN million / km</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>&lt; USD 500,000/route-km, converted at Inputs!B26 — state the rate and its date</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Línea Z Mexican precedent</t>
+        </is>
+      </c>
+      <c r="B21" s="24" t="n">
+        <v>60</v>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>MXN million / km</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>~18,000 MXN million / ~300 km  [PRESS — UNVERIFIED, must not carry a conclusion]</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>VERDICT TEST</t>
+        </is>
+      </c>
+      <c r="B23" s="25">
+        <f>IF(OR(D13="",B21=""),"pending inputs",IF(F13&lt;B21,"FAILS — even 100% capture at the highest cost of capital cannot support the Mexican precedent unit cost","review"))</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2473,7 +2842,7 @@
           <t>Divertible tonnage (bottom-up, commodity)</t>
         </is>
       </c>
-      <c r="B5" s="21">
+      <c r="B5" s="20">
         <f>Commodity!E15</f>
         <v/>
       </c>
@@ -2494,7 +2863,7 @@
           <t>Breakeven tonnage — most favourable case</t>
         </is>
       </c>
-      <c r="B6" s="21">
+      <c r="B6" s="20">
         <f>IF(COUNT(Breakeven!F8:F25)=0,"",MIN(Breakeven!F8:F25))</f>
         <v/>
       </c>
@@ -2515,7 +2884,7 @@
           <t>Breakeven tonnage — least favourable case</t>
         </is>
       </c>
-      <c r="B7" s="21">
+      <c r="B7" s="20">
         <f>IF(COUNT(Breakeven!F8:F25)=0,"",MAX(Breakeven!F8:F25))</f>
         <v/>
       </c>
@@ -2536,7 +2905,7 @@
           <t>Ratio: divertible / breakeven (favourable)</t>
         </is>
       </c>
-      <c r="B8" s="23">
+      <c r="B8" s="22">
         <f>IF(OR(B5="",B6="",B6=0),"",B5/B6)</f>
         <v/>
       </c>
@@ -2553,7 +2922,7 @@
           <t>Ratio: divertible / breakeven (unfavourable)</t>
         </is>
       </c>
-      <c r="B9" s="23">
+      <c r="B9" s="22">
         <f>IF(OR(B5="",B7="",B7=0),"",B5/B7)</f>
         <v/>
       </c>
@@ -2577,7 +2946,7 @@
           <t>Stop Rule 3 test</t>
         </is>
       </c>
-      <c r="B12" s="24">
+      <c r="B12" s="25">
         <f>IF(OR(B8="",B9=""),"pending inputs",IF(AND(B8&gt;1,B9&lt;1),"INDETERMINATE — scenarios straddle breakeven; field reconnaissance required",IF(B8&lt;1,"FAILS under every capital scenario",IF(B9&gt;1,"CLEARS under every capital scenario","review"))))</f>
         <v/>
       </c>

--- a/analysis/breakeven_model.xlsx
+++ b/analysis/breakeven_model.xlsx
@@ -115,7 +115,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -128,19 +128,18 @@
     <xf numFmtId="164" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="2" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -835,16 +834,22 @@
           <t>Light rehabilitation</t>
         </is>
       </c>
-      <c r="B7" s="8" t="n"/>
+      <c r="B7" s="8" t="n">
+        <v>6.9</v>
+      </c>
       <c r="C7" t="inlineStr">
         <is>
           <t>MXN million / km</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>wb-2020-serbia-railways-lcc T.11</t>
+        </is>
+      </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>UNESCAP guidance cited in brief: &lt; USD 500,000/route-km. Convert at B26 and cite</t>
+          <t>WB partial renewal (rail + ballast) 343/m @20 MXN/EUR. TRACK ONLY. Consistent with the UNESCAP &lt; USD 500,000/route-km figure the brief cites</t>
         </is>
       </c>
     </row>
@@ -854,14 +859,24 @@
           <t>Heavy rehabilitation</t>
         </is>
       </c>
-      <c r="B8" s="8" t="n"/>
+      <c r="B8" s="8" t="n">
+        <v>9.300000000000001</v>
+      </c>
       <c r="C8" t="inlineStr">
         <is>
           <t>MXN million / km</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" s="3" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>wb-2020-serbia-railways-lcc T.11</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>WB partial renewal (rail + sleeper exchange) 463/m @20 MXN/EUR. TRACK ONLY</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -869,14 +884,24 @@
           <t>Substantial reconstruction</t>
         </is>
       </c>
-      <c r="B9" s="8" t="n"/>
+      <c r="B9" s="8" t="n">
+        <v>14.3</v>
+      </c>
       <c r="C9" t="inlineStr">
         <is>
           <t>MXN million / km</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" s="3" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>wb-2020-serbia-railways-lcc T.11</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>WB general renewal + subsoil rehabilitation 716/m @20 MXN/EUR. TRACK ONLY. Currency NOT stated in the source; EUR assumed as the likelier of the two</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -914,16 +939,22 @@
           <t>Bridges / drainage / slope stabilisation — low</t>
         </is>
       </c>
-      <c r="B12" s="7" t="n"/>
+      <c r="B12" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="C12" t="inlineStr">
         <is>
           <t>MXN million</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>[UNSOURCED — SET 0]</t>
+        </is>
+      </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Dominant uncertainty. Carried as its own line with its own range, NOT buried in a percentage contingency. No public structure inventory is expected to exist</t>
+          <t>SET TO ZERO DELIBERATELY so the model computes a TRACK-ONLY LOWER BOUND. No public structure inventory is expected to exist for this line, and the World Bank unit costs above are track work only. Every result downstream is therefore an UNDERSTATEMENT of cost and an OVERSTATEMENT of viability. Replace with real figures before any decision</t>
         </is>
       </c>
     </row>
@@ -933,14 +964,24 @@
           <t>Bridges / drainage / slope stabilisation — high</t>
         </is>
       </c>
-      <c r="B13" s="7" t="n"/>
+      <c r="B13" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="C13" t="inlineStr">
         <is>
           <t>MXN million</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" s="3" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>[UNSOURCED — SET 0]</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Same. Material on this alignment: the Cañada sits where Sierra Madre Oriental and Sierra Madre del Sur folding converge, and CONANP already records slope instability, erosion and scour along the corridor's existing roads</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -960,7 +1001,7 @@
           <t>Asset life</t>
         </is>
       </c>
-      <c r="B15" s="10" t="n">
+      <c r="B15" s="11" t="n">
         <v>30</v>
       </c>
       <c r="C15" t="inlineStr">
@@ -981,7 +1022,7 @@
           <t>Cost of capital — case 1</t>
         </is>
       </c>
-      <c r="B16" s="11" t="n">
+      <c r="B16" s="12" t="n">
         <v>0.05</v>
       </c>
       <c r="C16" t="inlineStr">
@@ -1002,7 +1043,7 @@
           <t>Cost of capital — case 2</t>
         </is>
       </c>
-      <c r="B17" s="11" t="n">
+      <c r="B17" s="12" t="n">
         <v>0.06</v>
       </c>
       <c r="C17" t="inlineStr">
@@ -1023,7 +1064,7 @@
           <t>Cost of capital — case 3</t>
         </is>
       </c>
-      <c r="B18" s="11" t="n">
+      <c r="B18" s="12" t="n">
         <v>0.08</v>
       </c>
       <c r="C18" t="inlineStr">
@@ -1056,16 +1097,22 @@
           <t>Fixed O&amp;M (tonnage-independent)</t>
         </is>
       </c>
-      <c r="B20" s="7" t="n"/>
+      <c r="B20" s="13" t="n">
+        <v>0</v>
+      </c>
       <c r="C20" t="inlineStr">
         <is>
           <t>MXN million / yr</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>set 0 — see note</t>
+        </is>
+      </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>Signalling, admin, inspection, right-of-way security</t>
+          <t>MUST be 0 on the ARTF EBIT margin basis: ARTF's cost base already includes network operation and maintenance. Non-zero here double-counts</t>
         </is>
       </c>
     </row>
@@ -1075,16 +1122,22 @@
           <t>Variable O&amp;M per gross ton-km</t>
         </is>
       </c>
-      <c r="B21" s="12" t="n"/>
+      <c r="B21" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="C21" t="inlineStr">
         <is>
           <t>MXN / gross ton-km</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>set 0 — see note</t>
+        </is>
+      </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Track wear. This is what makes O&amp;M depend on the tonnage being solved for</t>
+          <t>Same reason. Track wear is already inside the 0.402 EBIT figure</t>
         </is>
       </c>
     </row>
@@ -1094,16 +1147,22 @@
           <t>Tare factor (gross / net tonnage)</t>
         </is>
       </c>
-      <c r="B22" s="8" t="n"/>
+      <c r="B22" s="15" t="n">
+        <v>0</v>
+      </c>
       <c r="C22" t="inlineStr">
         <is>
           <t>ratio</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>set 0 — see note</t>
+        </is>
+      </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Wagon tare + locomotive. Gross ton-km = net tons x (1 + tare) x km</t>
+          <t>Unused on the EBIT basis, since variable O&amp;M is 0</t>
         </is>
       </c>
     </row>
@@ -1125,7 +1184,7 @@
           <t>Contribution margin per net ton-km</t>
         </is>
       </c>
-      <c r="B24" s="12" t="n">
+      <c r="B24" s="16" t="n">
         <v>0.402</v>
       </c>
       <c r="C24" t="inlineStr">
@@ -1162,13 +1221,19 @@
           <t>MXN / USD rate</t>
         </is>
       </c>
-      <c r="B26" s="8" t="n"/>
+      <c r="B26" s="8" t="n">
+        <v>18.5</v>
+      </c>
       <c r="C26" t="inlineStr">
         <is>
           <t>MXN per USD</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>[ASSUMED]</t>
+        </is>
+      </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
           <t>State the rate AND its date. Required before any USD benchmark is used</t>
@@ -1181,14 +1246,26 @@
           <t>FX rate date</t>
         </is>
       </c>
-      <c r="B27" s="13" t="n"/>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>NOT SET — must be stated before use</t>
+        </is>
+      </c>
       <c r="C27" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" s="3" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>[REQUIRED]</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>An FX rate without its date is not a source</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1196,13 +1273,19 @@
           <t>Deflation base year (INEGI INPC)</t>
         </is>
       </c>
-      <c r="B28" s="10" t="n"/>
+      <c r="B28" s="11" t="n">
+        <v>2024</v>
+      </c>
       <c r="C28" t="inlineStr">
         <is>
           <t>yyyy</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>artf-2024-anuario</t>
+        </is>
+      </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
           <t>All money figures real in this year. Never mix nominal across years</t>
@@ -1224,11 +1307,11 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Payload per loaded articulated truck</t>
-        </is>
-      </c>
-      <c r="B30" s="14" t="n">
-        <v>27.5</v>
+          <t>Payload per articulated vehicle</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="n">
+        <v>19.1</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1237,12 +1320,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>[ASSUMPTION] 25–30 t</t>
+          <t>imt-pt179 Tabla 4.7</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>Bridge from vehicle counts to tonnage. This is an ASSUMPTION — show sensitivity</t>
+          <t>Weighted mean of IMT carga promedio (T3S2 13.2, T3S3 20.9, T3S2R4 30.1) at the observed terminus class mix. PRIMARY, but 2001 data — STALE</t>
         </is>
       </c>
     </row>
@@ -1252,8 +1335,8 @@
           <t>Empty-running share</t>
         </is>
       </c>
-      <c r="B31" s="15" t="n">
-        <v>0.4</v>
+      <c r="B31" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1262,12 +1345,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Prompt.md: ~30–50%</t>
+          <t>set 0 — see note</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>Raw truck counts are NOT loaded tonnage</t>
+          <t>MUST be 0 with the IMT payload above: carga promedio is averaged across observed vehicles and ALREADY nets out empty and partial running. A further discount double-counts</t>
         </is>
       </c>
     </row>
@@ -1277,7 +1360,7 @@
           <t>Observed articulated veh/day at corridor terminus</t>
         </is>
       </c>
-      <c r="B32" s="10" t="n">
+      <c r="B32" s="11" t="n">
         <v>500</v>
       </c>
       <c r="C32" t="inlineStr">
@@ -1302,7 +1385,7 @@
           <t>Variable O&amp;M — set 0 on the EBIT margin basis</t>
         </is>
       </c>
-      <c r="B33" s="16" t="n">
+      <c r="B33" s="14" t="n">
         <v>0</v>
       </c>
       <c r="C33" t="inlineStr">
@@ -1405,23 +1488,23 @@
         <f>Inputs!B7</f>
         <v/>
       </c>
-      <c r="C5" s="17">
+      <c r="C5" s="13">
         <f>IF(OR(B5="",Inputs!$B$5=""),"",B5*Inputs!$B$5)</f>
         <v/>
       </c>
-      <c r="D5" s="17">
+      <c r="D5" s="13">
         <f>Inputs!$B$12</f>
         <v/>
       </c>
-      <c r="E5" s="17">
+      <c r="E5" s="13">
         <f>Inputs!$B$13</f>
         <v/>
       </c>
-      <c r="F5" s="17">
+      <c r="F5" s="13">
         <f>IF(OR(C5="",D5=""),"",C5+D5)</f>
         <v/>
       </c>
-      <c r="G5" s="17">
+      <c r="G5" s="13">
         <f>IF(OR(C5="",E5=""),"",C5+E5)</f>
         <v/>
       </c>
@@ -1436,23 +1519,23 @@
         <f>Inputs!B8</f>
         <v/>
       </c>
-      <c r="C6" s="17">
+      <c r="C6" s="13">
         <f>IF(OR(B6="",Inputs!$B$5=""),"",B6*Inputs!$B$5)</f>
         <v/>
       </c>
-      <c r="D6" s="17">
+      <c r="D6" s="13">
         <f>Inputs!$B$12</f>
         <v/>
       </c>
-      <c r="E6" s="17">
+      <c r="E6" s="13">
         <f>Inputs!$B$13</f>
         <v/>
       </c>
-      <c r="F6" s="17">
+      <c r="F6" s="13">
         <f>IF(OR(C6="",D6=""),"",C6+D6)</f>
         <v/>
       </c>
-      <c r="G6" s="17">
+      <c r="G6" s="13">
         <f>IF(OR(C6="",E6=""),"",C6+E6)</f>
         <v/>
       </c>
@@ -1467,23 +1550,23 @@
         <f>Inputs!B9</f>
         <v/>
       </c>
-      <c r="C7" s="17">
+      <c r="C7" s="13">
         <f>IF(OR(B7="",Inputs!$B$5=""),"",B7*Inputs!$B$5)</f>
         <v/>
       </c>
-      <c r="D7" s="17">
+      <c r="D7" s="13">
         <f>Inputs!$B$12</f>
         <v/>
       </c>
-      <c r="E7" s="17">
+      <c r="E7" s="13">
         <f>Inputs!$B$13</f>
         <v/>
       </c>
-      <c r="F7" s="17">
+      <c r="F7" s="13">
         <f>IF(OR(C7="",D7=""),"",C7+D7)</f>
         <v/>
       </c>
-      <c r="G7" s="17">
+      <c r="G7" s="13">
         <f>IF(OR(C7="",E7=""),"",C7+E7)</f>
         <v/>
       </c>
@@ -1552,7 +1635,7 @@
           <t>Net contribution per net ton-km after track wear</t>
         </is>
       </c>
-      <c r="B5" s="16">
+      <c r="B5" s="14">
         <f>IF(OR(Inputs!B24="",Inputs!B21="",Inputs!B22=""),"",Inputs!B24-Inputs!B21*(1+Inputs!B22))</f>
         <v/>
       </c>
@@ -1609,27 +1692,27 @@
           <t>Light rehab (low structures)</t>
         </is>
       </c>
-      <c r="B8" s="17">
+      <c r="B8" s="13">
         <f>Capital!F5</f>
         <v/>
       </c>
-      <c r="C8" s="19">
+      <c r="C8" s="17">
         <f>Inputs!$B$16</f>
         <v/>
       </c>
-      <c r="D8" s="17">
+      <c r="D8" s="13">
         <f>IF(OR(B8="",C8="",Inputs!$B$15=""),"",-PMT(C8,Inputs!$B$15,B8))</f>
         <v/>
       </c>
-      <c r="E8" s="17">
+      <c r="E8" s="13">
         <f>Inputs!$B$20</f>
         <v/>
       </c>
-      <c r="F8" s="20">
+      <c r="F8" s="19">
         <f>IF(OR(D8="",E8="",$B$5="",$B$5&lt;=0,Inputs!$B$5=""),"",(D8+E8)*1000000/(Inputs!$B$5*$B$5))</f>
         <v/>
       </c>
-      <c r="G8" s="20">
+      <c r="G8" s="19">
         <f>IF(OR(F8="",Inputs!$B$30="",Inputs!$B$30=0),"",F8/(Inputs!$B$30*365*2))</f>
         <v/>
       </c>
@@ -1640,27 +1723,27 @@
           <t>Light rehab (low structures)</t>
         </is>
       </c>
-      <c r="B9" s="17">
+      <c r="B9" s="13">
         <f>Capital!F5</f>
         <v/>
       </c>
-      <c r="C9" s="19">
+      <c r="C9" s="17">
         <f>Inputs!$B$17</f>
         <v/>
       </c>
-      <c r="D9" s="17">
+      <c r="D9" s="13">
         <f>IF(OR(B9="",C9="",Inputs!$B$15=""),"",-PMT(C9,Inputs!$B$15,B9))</f>
         <v/>
       </c>
-      <c r="E9" s="17">
+      <c r="E9" s="13">
         <f>Inputs!$B$20</f>
         <v/>
       </c>
-      <c r="F9" s="20">
+      <c r="F9" s="19">
         <f>IF(OR(D9="",E9="",$B$5="",$B$5&lt;=0,Inputs!$B$5=""),"",(D9+E9)*1000000/(Inputs!$B$5*$B$5))</f>
         <v/>
       </c>
-      <c r="G9" s="20">
+      <c r="G9" s="19">
         <f>IF(OR(F9="",Inputs!$B$30="",Inputs!$B$30=0),"",F9/(Inputs!$B$30*365*2))</f>
         <v/>
       </c>
@@ -1671,27 +1754,27 @@
           <t>Light rehab (low structures)</t>
         </is>
       </c>
-      <c r="B10" s="17">
+      <c r="B10" s="13">
         <f>Capital!F5</f>
         <v/>
       </c>
-      <c r="C10" s="19">
+      <c r="C10" s="17">
         <f>Inputs!$B$18</f>
         <v/>
       </c>
-      <c r="D10" s="17">
+      <c r="D10" s="13">
         <f>IF(OR(B10="",C10="",Inputs!$B$15=""),"",-PMT(C10,Inputs!$B$15,B10))</f>
         <v/>
       </c>
-      <c r="E10" s="17">
+      <c r="E10" s="13">
         <f>Inputs!$B$20</f>
         <v/>
       </c>
-      <c r="F10" s="20">
+      <c r="F10" s="19">
         <f>IF(OR(D10="",E10="",$B$5="",$B$5&lt;=0,Inputs!$B$5=""),"",(D10+E10)*1000000/(Inputs!$B$5*$B$5))</f>
         <v/>
       </c>
-      <c r="G10" s="20">
+      <c r="G10" s="19">
         <f>IF(OR(F10="",Inputs!$B$30="",Inputs!$B$30=0),"",F10/(Inputs!$B$30*365*2))</f>
         <v/>
       </c>
@@ -1702,27 +1785,27 @@
           <t>Light rehab (high structures)</t>
         </is>
       </c>
-      <c r="B11" s="17">
+      <c r="B11" s="13">
         <f>Capital!G5</f>
         <v/>
       </c>
-      <c r="C11" s="19">
+      <c r="C11" s="17">
         <f>Inputs!$B$16</f>
         <v/>
       </c>
-      <c r="D11" s="17">
+      <c r="D11" s="13">
         <f>IF(OR(B11="",C11="",Inputs!$B$15=""),"",-PMT(C11,Inputs!$B$15,B11))</f>
         <v/>
       </c>
-      <c r="E11" s="17">
+      <c r="E11" s="13">
         <f>Inputs!$B$20</f>
         <v/>
       </c>
-      <c r="F11" s="20">
+      <c r="F11" s="19">
         <f>IF(OR(D11="",E11="",$B$5="",$B$5&lt;=0,Inputs!$B$5=""),"",(D11+E11)*1000000/(Inputs!$B$5*$B$5))</f>
         <v/>
       </c>
-      <c r="G11" s="20">
+      <c r="G11" s="19">
         <f>IF(OR(F11="",Inputs!$B$30="",Inputs!$B$30=0),"",F11/(Inputs!$B$30*365*2))</f>
         <v/>
       </c>
@@ -1733,27 +1816,27 @@
           <t>Light rehab (high structures)</t>
         </is>
       </c>
-      <c r="B12" s="17">
+      <c r="B12" s="13">
         <f>Capital!G5</f>
         <v/>
       </c>
-      <c r="C12" s="19">
+      <c r="C12" s="17">
         <f>Inputs!$B$17</f>
         <v/>
       </c>
-      <c r="D12" s="17">
+      <c r="D12" s="13">
         <f>IF(OR(B12="",C12="",Inputs!$B$15=""),"",-PMT(C12,Inputs!$B$15,B12))</f>
         <v/>
       </c>
-      <c r="E12" s="17">
+      <c r="E12" s="13">
         <f>Inputs!$B$20</f>
         <v/>
       </c>
-      <c r="F12" s="20">
+      <c r="F12" s="19">
         <f>IF(OR(D12="",E12="",$B$5="",$B$5&lt;=0,Inputs!$B$5=""),"",(D12+E12)*1000000/(Inputs!$B$5*$B$5))</f>
         <v/>
       </c>
-      <c r="G12" s="20">
+      <c r="G12" s="19">
         <f>IF(OR(F12="",Inputs!$B$30="",Inputs!$B$30=0),"",F12/(Inputs!$B$30*365*2))</f>
         <v/>
       </c>
@@ -1764,27 +1847,27 @@
           <t>Light rehab (high structures)</t>
         </is>
       </c>
-      <c r="B13" s="17">
+      <c r="B13" s="13">
         <f>Capital!G5</f>
         <v/>
       </c>
-      <c r="C13" s="19">
+      <c r="C13" s="17">
         <f>Inputs!$B$18</f>
         <v/>
       </c>
-      <c r="D13" s="17">
+      <c r="D13" s="13">
         <f>IF(OR(B13="",C13="",Inputs!$B$15=""),"",-PMT(C13,Inputs!$B$15,B13))</f>
         <v/>
       </c>
-      <c r="E13" s="17">
+      <c r="E13" s="13">
         <f>Inputs!$B$20</f>
         <v/>
       </c>
-      <c r="F13" s="20">
+      <c r="F13" s="19">
         <f>IF(OR(D13="",E13="",$B$5="",$B$5&lt;=0,Inputs!$B$5=""),"",(D13+E13)*1000000/(Inputs!$B$5*$B$5))</f>
         <v/>
       </c>
-      <c r="G13" s="20">
+      <c r="G13" s="19">
         <f>IF(OR(F13="",Inputs!$B$30="",Inputs!$B$30=0),"",F13/(Inputs!$B$30*365*2))</f>
         <v/>
       </c>
@@ -1795,27 +1878,27 @@
           <t>Heavy rehab (low structures)</t>
         </is>
       </c>
-      <c r="B14" s="17">
+      <c r="B14" s="13">
         <f>Capital!F6</f>
         <v/>
       </c>
-      <c r="C14" s="19">
+      <c r="C14" s="17">
         <f>Inputs!$B$16</f>
         <v/>
       </c>
-      <c r="D14" s="17">
+      <c r="D14" s="13">
         <f>IF(OR(B14="",C14="",Inputs!$B$15=""),"",-PMT(C14,Inputs!$B$15,B14))</f>
         <v/>
       </c>
-      <c r="E14" s="17">
+      <c r="E14" s="13">
         <f>Inputs!$B$20</f>
         <v/>
       </c>
-      <c r="F14" s="20">
+      <c r="F14" s="19">
         <f>IF(OR(D14="",E14="",$B$5="",$B$5&lt;=0,Inputs!$B$5=""),"",(D14+E14)*1000000/(Inputs!$B$5*$B$5))</f>
         <v/>
       </c>
-      <c r="G14" s="20">
+      <c r="G14" s="19">
         <f>IF(OR(F14="",Inputs!$B$30="",Inputs!$B$30=0),"",F14/(Inputs!$B$30*365*2))</f>
         <v/>
       </c>
@@ -1826,27 +1909,27 @@
           <t>Heavy rehab (low structures)</t>
         </is>
       </c>
-      <c r="B15" s="17">
+      <c r="B15" s="13">
         <f>Capital!F6</f>
         <v/>
       </c>
-      <c r="C15" s="19">
+      <c r="C15" s="17">
         <f>Inputs!$B$17</f>
         <v/>
       </c>
-      <c r="D15" s="17">
+      <c r="D15" s="13">
         <f>IF(OR(B15="",C15="",Inputs!$B$15=""),"",-PMT(C15,Inputs!$B$15,B15))</f>
         <v/>
       </c>
-      <c r="E15" s="17">
+      <c r="E15" s="13">
         <f>Inputs!$B$20</f>
         <v/>
       </c>
-      <c r="F15" s="20">
+      <c r="F15" s="19">
         <f>IF(OR(D15="",E15="",$B$5="",$B$5&lt;=0,Inputs!$B$5=""),"",(D15+E15)*1000000/(Inputs!$B$5*$B$5))</f>
         <v/>
       </c>
-      <c r="G15" s="20">
+      <c r="G15" s="19">
         <f>IF(OR(F15="",Inputs!$B$30="",Inputs!$B$30=0),"",F15/(Inputs!$B$30*365*2))</f>
         <v/>
       </c>
@@ -1857,27 +1940,27 @@
           <t>Heavy rehab (low structures)</t>
         </is>
       </c>
-      <c r="B16" s="17">
+      <c r="B16" s="13">
         <f>Capital!F6</f>
         <v/>
       </c>
-      <c r="C16" s="19">
+      <c r="C16" s="17">
         <f>Inputs!$B$18</f>
         <v/>
       </c>
-      <c r="D16" s="17">
+      <c r="D16" s="13">
         <f>IF(OR(B16="",C16="",Inputs!$B$15=""),"",-PMT(C16,Inputs!$B$15,B16))</f>
         <v/>
       </c>
-      <c r="E16" s="17">
+      <c r="E16" s="13">
         <f>Inputs!$B$20</f>
         <v/>
       </c>
-      <c r="F16" s="20">
+      <c r="F16" s="19">
         <f>IF(OR(D16="",E16="",$B$5="",$B$5&lt;=0,Inputs!$B$5=""),"",(D16+E16)*1000000/(Inputs!$B$5*$B$5))</f>
         <v/>
       </c>
-      <c r="G16" s="20">
+      <c r="G16" s="19">
         <f>IF(OR(F16="",Inputs!$B$30="",Inputs!$B$30=0),"",F16/(Inputs!$B$30*365*2))</f>
         <v/>
       </c>
@@ -1888,27 +1971,27 @@
           <t>Heavy rehab (high structures)</t>
         </is>
       </c>
-      <c r="B17" s="17">
+      <c r="B17" s="13">
         <f>Capital!G6</f>
         <v/>
       </c>
-      <c r="C17" s="19">
+      <c r="C17" s="17">
         <f>Inputs!$B$16</f>
         <v/>
       </c>
-      <c r="D17" s="17">
+      <c r="D17" s="13">
         <f>IF(OR(B17="",C17="",Inputs!$B$15=""),"",-PMT(C17,Inputs!$B$15,B17))</f>
         <v/>
       </c>
-      <c r="E17" s="17">
+      <c r="E17" s="13">
         <f>Inputs!$B$20</f>
         <v/>
       </c>
-      <c r="F17" s="20">
+      <c r="F17" s="19">
         <f>IF(OR(D17="",E17="",$B$5="",$B$5&lt;=0,Inputs!$B$5=""),"",(D17+E17)*1000000/(Inputs!$B$5*$B$5))</f>
         <v/>
       </c>
-      <c r="G17" s="20">
+      <c r="G17" s="19">
         <f>IF(OR(F17="",Inputs!$B$30="",Inputs!$B$30=0),"",F17/(Inputs!$B$30*365*2))</f>
         <v/>
       </c>
@@ -1919,27 +2002,27 @@
           <t>Heavy rehab (high structures)</t>
         </is>
       </c>
-      <c r="B18" s="17">
+      <c r="B18" s="13">
         <f>Capital!G6</f>
         <v/>
       </c>
-      <c r="C18" s="19">
+      <c r="C18" s="17">
         <f>Inputs!$B$17</f>
         <v/>
       </c>
-      <c r="D18" s="17">
+      <c r="D18" s="13">
         <f>IF(OR(B18="",C18="",Inputs!$B$15=""),"",-PMT(C18,Inputs!$B$15,B18))</f>
         <v/>
       </c>
-      <c r="E18" s="17">
+      <c r="E18" s="13">
         <f>Inputs!$B$20</f>
         <v/>
       </c>
-      <c r="F18" s="20">
+      <c r="F18" s="19">
         <f>IF(OR(D18="",E18="",$B$5="",$B$5&lt;=0,Inputs!$B$5=""),"",(D18+E18)*1000000/(Inputs!$B$5*$B$5))</f>
         <v/>
       </c>
-      <c r="G18" s="20">
+      <c r="G18" s="19">
         <f>IF(OR(F18="",Inputs!$B$30="",Inputs!$B$30=0),"",F18/(Inputs!$B$30*365*2))</f>
         <v/>
       </c>
@@ -1950,27 +2033,27 @@
           <t>Heavy rehab (high structures)</t>
         </is>
       </c>
-      <c r="B19" s="17">
+      <c r="B19" s="13">
         <f>Capital!G6</f>
         <v/>
       </c>
-      <c r="C19" s="19">
+      <c r="C19" s="17">
         <f>Inputs!$B$18</f>
         <v/>
       </c>
-      <c r="D19" s="17">
+      <c r="D19" s="13">
         <f>IF(OR(B19="",C19="",Inputs!$B$15=""),"",-PMT(C19,Inputs!$B$15,B19))</f>
         <v/>
       </c>
-      <c r="E19" s="17">
+      <c r="E19" s="13">
         <f>Inputs!$B$20</f>
         <v/>
       </c>
-      <c r="F19" s="20">
+      <c r="F19" s="19">
         <f>IF(OR(D19="",E19="",$B$5="",$B$5&lt;=0,Inputs!$B$5=""),"",(D19+E19)*1000000/(Inputs!$B$5*$B$5))</f>
         <v/>
       </c>
-      <c r="G19" s="20">
+      <c r="G19" s="19">
         <f>IF(OR(F19="",Inputs!$B$30="",Inputs!$B$30=0),"",F19/(Inputs!$B$30*365*2))</f>
         <v/>
       </c>
@@ -1981,27 +2064,27 @@
           <t>Substantial recon (low struct.)</t>
         </is>
       </c>
-      <c r="B20" s="17">
+      <c r="B20" s="13">
         <f>Capital!F7</f>
         <v/>
       </c>
-      <c r="C20" s="19">
+      <c r="C20" s="17">
         <f>Inputs!$B$16</f>
         <v/>
       </c>
-      <c r="D20" s="17">
+      <c r="D20" s="13">
         <f>IF(OR(B20="",C20="",Inputs!$B$15=""),"",-PMT(C20,Inputs!$B$15,B20))</f>
         <v/>
       </c>
-      <c r="E20" s="17">
+      <c r="E20" s="13">
         <f>Inputs!$B$20</f>
         <v/>
       </c>
-      <c r="F20" s="20">
+      <c r="F20" s="19">
         <f>IF(OR(D20="",E20="",$B$5="",$B$5&lt;=0,Inputs!$B$5=""),"",(D20+E20)*1000000/(Inputs!$B$5*$B$5))</f>
         <v/>
       </c>
-      <c r="G20" s="20">
+      <c r="G20" s="19">
         <f>IF(OR(F20="",Inputs!$B$30="",Inputs!$B$30=0),"",F20/(Inputs!$B$30*365*2))</f>
         <v/>
       </c>
@@ -2012,27 +2095,27 @@
           <t>Substantial recon (low struct.)</t>
         </is>
       </c>
-      <c r="B21" s="17">
+      <c r="B21" s="13">
         <f>Capital!F7</f>
         <v/>
       </c>
-      <c r="C21" s="19">
+      <c r="C21" s="17">
         <f>Inputs!$B$17</f>
         <v/>
       </c>
-      <c r="D21" s="17">
+      <c r="D21" s="13">
         <f>IF(OR(B21="",C21="",Inputs!$B$15=""),"",-PMT(C21,Inputs!$B$15,B21))</f>
         <v/>
       </c>
-      <c r="E21" s="17">
+      <c r="E21" s="13">
         <f>Inputs!$B$20</f>
         <v/>
       </c>
-      <c r="F21" s="20">
+      <c r="F21" s="19">
         <f>IF(OR(D21="",E21="",$B$5="",$B$5&lt;=0,Inputs!$B$5=""),"",(D21+E21)*1000000/(Inputs!$B$5*$B$5))</f>
         <v/>
       </c>
-      <c r="G21" s="20">
+      <c r="G21" s="19">
         <f>IF(OR(F21="",Inputs!$B$30="",Inputs!$B$30=0),"",F21/(Inputs!$B$30*365*2))</f>
         <v/>
       </c>
@@ -2043,27 +2126,27 @@
           <t>Substantial recon (low struct.)</t>
         </is>
       </c>
-      <c r="B22" s="17">
+      <c r="B22" s="13">
         <f>Capital!F7</f>
         <v/>
       </c>
-      <c r="C22" s="19">
+      <c r="C22" s="17">
         <f>Inputs!$B$18</f>
         <v/>
       </c>
-      <c r="D22" s="17">
+      <c r="D22" s="13">
         <f>IF(OR(B22="",C22="",Inputs!$B$15=""),"",-PMT(C22,Inputs!$B$15,B22))</f>
         <v/>
       </c>
-      <c r="E22" s="17">
+      <c r="E22" s="13">
         <f>Inputs!$B$20</f>
         <v/>
       </c>
-      <c r="F22" s="20">
+      <c r="F22" s="19">
         <f>IF(OR(D22="",E22="",$B$5="",$B$5&lt;=0,Inputs!$B$5=""),"",(D22+E22)*1000000/(Inputs!$B$5*$B$5))</f>
         <v/>
       </c>
-      <c r="G22" s="20">
+      <c r="G22" s="19">
         <f>IF(OR(F22="",Inputs!$B$30="",Inputs!$B$30=0),"",F22/(Inputs!$B$30*365*2))</f>
         <v/>
       </c>
@@ -2074,27 +2157,27 @@
           <t>Substantial recon (high struct.)</t>
         </is>
       </c>
-      <c r="B23" s="17">
+      <c r="B23" s="13">
         <f>Capital!G7</f>
         <v/>
       </c>
-      <c r="C23" s="19">
+      <c r="C23" s="17">
         <f>Inputs!$B$16</f>
         <v/>
       </c>
-      <c r="D23" s="17">
+      <c r="D23" s="13">
         <f>IF(OR(B23="",C23="",Inputs!$B$15=""),"",-PMT(C23,Inputs!$B$15,B23))</f>
         <v/>
       </c>
-      <c r="E23" s="17">
+      <c r="E23" s="13">
         <f>Inputs!$B$20</f>
         <v/>
       </c>
-      <c r="F23" s="20">
+      <c r="F23" s="19">
         <f>IF(OR(D23="",E23="",$B$5="",$B$5&lt;=0,Inputs!$B$5=""),"",(D23+E23)*1000000/(Inputs!$B$5*$B$5))</f>
         <v/>
       </c>
-      <c r="G23" s="20">
+      <c r="G23" s="19">
         <f>IF(OR(F23="",Inputs!$B$30="",Inputs!$B$30=0),"",F23/(Inputs!$B$30*365*2))</f>
         <v/>
       </c>
@@ -2105,27 +2188,27 @@
           <t>Substantial recon (high struct.)</t>
         </is>
       </c>
-      <c r="B24" s="17">
+      <c r="B24" s="13">
         <f>Capital!G7</f>
         <v/>
       </c>
-      <c r="C24" s="19">
+      <c r="C24" s="17">
         <f>Inputs!$B$17</f>
         <v/>
       </c>
-      <c r="D24" s="17">
+      <c r="D24" s="13">
         <f>IF(OR(B24="",C24="",Inputs!$B$15=""),"",-PMT(C24,Inputs!$B$15,B24))</f>
         <v/>
       </c>
-      <c r="E24" s="17">
+      <c r="E24" s="13">
         <f>Inputs!$B$20</f>
         <v/>
       </c>
-      <c r="F24" s="20">
+      <c r="F24" s="19">
         <f>IF(OR(D24="",E24="",$B$5="",$B$5&lt;=0,Inputs!$B$5=""),"",(D24+E24)*1000000/(Inputs!$B$5*$B$5))</f>
         <v/>
       </c>
-      <c r="G24" s="20">
+      <c r="G24" s="19">
         <f>IF(OR(F24="",Inputs!$B$30="",Inputs!$B$30=0),"",F24/(Inputs!$B$30*365*2))</f>
         <v/>
       </c>
@@ -2136,27 +2219,27 @@
           <t>Substantial recon (high struct.)</t>
         </is>
       </c>
-      <c r="B25" s="17">
+      <c r="B25" s="13">
         <f>Capital!G7</f>
         <v/>
       </c>
-      <c r="C25" s="19">
+      <c r="C25" s="17">
         <f>Inputs!$B$18</f>
         <v/>
       </c>
-      <c r="D25" s="17">
+      <c r="D25" s="13">
         <f>IF(OR(B25="",C25="",Inputs!$B$15=""),"",-PMT(C25,Inputs!$B$15,B25))</f>
         <v/>
       </c>
-      <c r="E25" s="17">
+      <c r="E25" s="13">
         <f>Inputs!$B$20</f>
         <v/>
       </c>
-      <c r="F25" s="20">
+      <c r="F25" s="19">
         <f>IF(OR(D25="",E25="",$B$5="",$B$5&lt;=0,Inputs!$B$5=""),"",(D25+E25)*1000000/(Inputs!$B$5*$B$5))</f>
         <v/>
       </c>
-      <c r="G25" s="20">
+      <c r="G25" s="19">
         <f>IF(OR(F25="",Inputs!$B$30="",Inputs!$B$30=0),"",F25/(Inputs!$B$30*365*2))</f>
         <v/>
       </c>
@@ -2254,9 +2337,9 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="C5" s="13" t="n"/>
-      <c r="D5" s="11" t="n"/>
-      <c r="E5" s="20">
+      <c r="C5" s="20" t="n"/>
+      <c r="D5" s="12" t="n"/>
+      <c r="E5" s="19">
         <f>IF(OR(C5="",D5=""),"",C5*D5)</f>
         <v/>
       </c>
@@ -2272,9 +2355,9 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="C6" s="13" t="n"/>
-      <c r="D6" s="11" t="n"/>
-      <c r="E6" s="20">
+      <c r="C6" s="20" t="n"/>
+      <c r="D6" s="12" t="n"/>
+      <c r="E6" s="19">
         <f>IF(OR(C6="",D6=""),"",C6*D6)</f>
         <v/>
       </c>
@@ -2290,9 +2373,9 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="C7" s="13" t="n"/>
-      <c r="D7" s="11" t="n"/>
-      <c r="E7" s="20">
+      <c r="C7" s="20" t="n"/>
+      <c r="D7" s="12" t="n"/>
+      <c r="E7" s="19">
         <f>IF(OR(C7="",D7=""),"",C7*D7)</f>
         <v/>
       </c>
@@ -2308,9 +2391,9 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="C8" s="13" t="n"/>
-      <c r="D8" s="11" t="n"/>
-      <c r="E8" s="20">
+      <c r="C8" s="20" t="n"/>
+      <c r="D8" s="12" t="n"/>
+      <c r="E8" s="19">
         <f>IF(OR(C8="",D8=""),"",C8*D8)</f>
         <v/>
       </c>
@@ -2326,9 +2409,9 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="C9" s="13" t="n"/>
-      <c r="D9" s="11" t="n"/>
-      <c r="E9" s="20">
+      <c r="C9" s="20" t="n"/>
+      <c r="D9" s="12" t="n"/>
+      <c r="E9" s="19">
         <f>IF(OR(C9="",D9=""),"",C9*D9)</f>
         <v/>
       </c>
@@ -2344,9 +2427,9 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="C10" s="13" t="n"/>
-      <c r="D10" s="11" t="n"/>
-      <c r="E10" s="20">
+      <c r="C10" s="20" t="n"/>
+      <c r="D10" s="12" t="n"/>
+      <c r="E10" s="19">
         <f>IF(OR(C10="",D10=""),"",C10*D10)</f>
         <v/>
       </c>
@@ -2362,9 +2445,9 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="C11" s="13" t="n"/>
-      <c r="D11" s="11" t="n"/>
-      <c r="E11" s="20">
+      <c r="C11" s="20" t="n"/>
+      <c r="D11" s="12" t="n"/>
+      <c r="E11" s="19">
         <f>IF(OR(C11="",D11=""),"",C11*D11)</f>
         <v/>
       </c>
@@ -2380,9 +2463,9 @@
           <t>low</t>
         </is>
       </c>
-      <c r="C12" s="13" t="n"/>
-      <c r="D12" s="11" t="n"/>
-      <c r="E12" s="20">
+      <c r="C12" s="20" t="n"/>
+      <c r="D12" s="12" t="n"/>
+      <c r="E12" s="19">
         <f>IF(OR(C12="",D12=""),"",C12*D12)</f>
         <v/>
       </c>
@@ -2398,9 +2481,9 @@
           <t>low</t>
         </is>
       </c>
-      <c r="C13" s="13" t="n"/>
-      <c r="D13" s="11" t="n"/>
-      <c r="E13" s="20">
+      <c r="C13" s="20" t="n"/>
+      <c r="D13" s="12" t="n"/>
+      <c r="E13" s="19">
         <f>IF(OR(C13="",D13=""),"",C13*D13)</f>
         <v/>
       </c>
@@ -2416,9 +2499,9 @@
           <t>low</t>
         </is>
       </c>
-      <c r="C14" s="13" t="n"/>
-      <c r="D14" s="11" t="n"/>
-      <c r="E14" s="20">
+      <c r="C14" s="20" t="n"/>
+      <c r="D14" s="12" t="n"/>
+      <c r="E14" s="19">
         <f>IF(OR(C14="",D14=""),"",C14*D14)</f>
         <v/>
       </c>
@@ -2497,7 +2580,7 @@
           <t>Articulated veh/day, both directions</t>
         </is>
       </c>
-      <c r="B5" s="20">
+      <c r="B5" s="19">
         <f>Inputs!B32</f>
         <v/>
       </c>
@@ -2518,7 +2601,7 @@
           <t>Loaded share</t>
         </is>
       </c>
-      <c r="B6" s="22">
+      <c r="B6" s="15">
         <f>IF(Inputs!B31="","",1-Inputs!B31)</f>
         <v/>
       </c>
@@ -2539,7 +2622,7 @@
           <t>Payload per loaded truck</t>
         </is>
       </c>
-      <c r="B7" s="22">
+      <c r="B7" s="15">
         <f>Inputs!B30</f>
         <v/>
       </c>
@@ -2560,7 +2643,7 @@
           <t>Corridor tonnage</t>
         </is>
       </c>
-      <c r="B8" s="20">
+      <c r="B8" s="19">
         <f>IF(OR(B5="",B6="",B7=""),"",B5*B6*B7*365)</f>
         <v/>
       </c>
@@ -2622,101 +2705,101 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="23" t="n">
+      <c r="A13" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="B13" s="20">
+      <c r="B13" s="19">
         <f>IF($B$8="","",$B$8*A13)</f>
         <v/>
       </c>
-      <c r="C13" s="17">
+      <c r="C13" s="13">
         <f>IF(OR(B13="",Inputs!$B$24="",Inputs!$B$5=""),"",B13*Inputs!$B$5*Inputs!$B$24/1000000)</f>
         <v/>
       </c>
-      <c r="D13" s="17">
+      <c r="D13" s="13">
         <f>IF(OR($C13="",Inputs!$B$16="",Inputs!$B$15="",Inputs!$B$5=""),"",$C13*((1-(1+Inputs!$B$16)^-Inputs!$B$15)/Inputs!$B$16)/Inputs!$B$5)</f>
         <v/>
       </c>
-      <c r="E13" s="17">
+      <c r="E13" s="13">
         <f>IF(OR($C13="",Inputs!$B$17="",Inputs!$B$15="",Inputs!$B$5=""),"",$C13*((1-(1+Inputs!$B$17)^-Inputs!$B$15)/Inputs!$B$17)/Inputs!$B$5)</f>
         <v/>
       </c>
-      <c r="F13" s="17">
+      <c r="F13" s="13">
         <f>IF(OR($C13="",Inputs!$B$18="",Inputs!$B$15="",Inputs!$B$5=""),"",$C13*((1-(1+Inputs!$B$18)^-Inputs!$B$15)/Inputs!$B$18)/Inputs!$B$5)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="23" t="n">
+      <c r="A14" s="22" t="n">
         <v>0.5</v>
       </c>
-      <c r="B14" s="20">
+      <c r="B14" s="19">
         <f>IF($B$8="","",$B$8*A14)</f>
         <v/>
       </c>
-      <c r="C14" s="17">
+      <c r="C14" s="13">
         <f>IF(OR(B14="",Inputs!$B$24="",Inputs!$B$5=""),"",B14*Inputs!$B$5*Inputs!$B$24/1000000)</f>
         <v/>
       </c>
-      <c r="D14" s="17">
+      <c r="D14" s="13">
         <f>IF(OR($C14="",Inputs!$B$16="",Inputs!$B$15="",Inputs!$B$5=""),"",$C14*((1-(1+Inputs!$B$16)^-Inputs!$B$15)/Inputs!$B$16)/Inputs!$B$5)</f>
         <v/>
       </c>
-      <c r="E14" s="17">
+      <c r="E14" s="13">
         <f>IF(OR($C14="",Inputs!$B$17="",Inputs!$B$15="",Inputs!$B$5=""),"",$C14*((1-(1+Inputs!$B$17)^-Inputs!$B$15)/Inputs!$B$17)/Inputs!$B$5)</f>
         <v/>
       </c>
-      <c r="F14" s="17">
+      <c r="F14" s="13">
         <f>IF(OR($C14="",Inputs!$B$18="",Inputs!$B$15="",Inputs!$B$5=""),"",$C14*((1-(1+Inputs!$B$18)^-Inputs!$B$15)/Inputs!$B$18)/Inputs!$B$5)</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="23" t="n">
+      <c r="A15" s="22" t="n">
         <v>0.3</v>
       </c>
-      <c r="B15" s="20">
+      <c r="B15" s="19">
         <f>IF($B$8="","",$B$8*A15)</f>
         <v/>
       </c>
-      <c r="C15" s="17">
+      <c r="C15" s="13">
         <f>IF(OR(B15="",Inputs!$B$24="",Inputs!$B$5=""),"",B15*Inputs!$B$5*Inputs!$B$24/1000000)</f>
         <v/>
       </c>
-      <c r="D15" s="17">
+      <c r="D15" s="13">
         <f>IF(OR($C15="",Inputs!$B$16="",Inputs!$B$15="",Inputs!$B$5=""),"",$C15*((1-(1+Inputs!$B$16)^-Inputs!$B$15)/Inputs!$B$16)/Inputs!$B$5)</f>
         <v/>
       </c>
-      <c r="E15" s="17">
+      <c r="E15" s="13">
         <f>IF(OR($C15="",Inputs!$B$17="",Inputs!$B$15="",Inputs!$B$5=""),"",$C15*((1-(1+Inputs!$B$17)^-Inputs!$B$15)/Inputs!$B$17)/Inputs!$B$5)</f>
         <v/>
       </c>
-      <c r="F15" s="17">
+      <c r="F15" s="13">
         <f>IF(OR($C15="",Inputs!$B$18="",Inputs!$B$15="",Inputs!$B$5=""),"",$C15*((1-(1+Inputs!$B$18)^-Inputs!$B$15)/Inputs!$B$18)/Inputs!$B$5)</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="23" t="n">
+      <c r="A16" s="22" t="n">
         <v>0.15</v>
       </c>
-      <c r="B16" s="20">
+      <c r="B16" s="19">
         <f>IF($B$8="","",$B$8*A16)</f>
         <v/>
       </c>
-      <c r="C16" s="17">
+      <c r="C16" s="13">
         <f>IF(OR(B16="",Inputs!$B$24="",Inputs!$B$5=""),"",B16*Inputs!$B$5*Inputs!$B$24/1000000)</f>
         <v/>
       </c>
-      <c r="D16" s="17">
+      <c r="D16" s="13">
         <f>IF(OR($C16="",Inputs!$B$16="",Inputs!$B$15="",Inputs!$B$5=""),"",$C16*((1-(1+Inputs!$B$16)^-Inputs!$B$15)/Inputs!$B$16)/Inputs!$B$5)</f>
         <v/>
       </c>
-      <c r="E16" s="17">
+      <c r="E16" s="13">
         <f>IF(OR($C16="",Inputs!$B$17="",Inputs!$B$15="",Inputs!$B$5=""),"",$C16*((1-(1+Inputs!$B$17)^-Inputs!$B$15)/Inputs!$B$17)/Inputs!$B$5)</f>
         <v/>
       </c>
-      <c r="F16" s="17">
+      <c r="F16" s="13">
         <f>IF(OR($C16="",Inputs!$B$18="",Inputs!$B$15="",Inputs!$B$5=""),"",$C16*((1-(1+Inputs!$B$18)^-Inputs!$B$15)/Inputs!$B$18)/Inputs!$B$5)</f>
         <v/>
       </c>
@@ -2734,7 +2817,7 @@
           <t>UNESCAP light rehabilitation</t>
         </is>
       </c>
-      <c r="B20" s="22">
+      <c r="B20" s="15">
         <f>IF(Inputs!B26="","",0.5*Inputs!B26)</f>
         <v/>
       </c>
@@ -2755,7 +2838,7 @@
           <t>Línea Z Mexican precedent</t>
         </is>
       </c>
-      <c r="B21" s="24" t="n">
+      <c r="B21" s="23" t="n">
         <v>60</v>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -2775,7 +2858,7 @@
           <t>VERDICT TEST</t>
         </is>
       </c>
-      <c r="B23" s="25">
+      <c r="B23" s="24">
         <f>IF(OR(D13="",B21=""),"pending inputs",IF(F13&lt;B21,"FAILS — even 100% capture at the highest cost of capital cannot support the Mexican precedent unit cost","review"))</f>
         <v/>
       </c>
@@ -2791,7 +2874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -2839,11 +2922,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Divertible tonnage (bottom-up, commodity)</t>
-        </is>
-      </c>
-      <c r="B5" s="20">
-        <f>Commodity!E15</f>
+          <t>Corridor tonnage, ALL articulated freight</t>
+        </is>
+      </c>
+      <c r="B5" s="19">
+        <f>Supportable!B8</f>
         <v/>
       </c>
       <c r="C5" t="inlineStr">
@@ -2853,108 +2936,178 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Commodity sheet</t>
+          <t>aforo 2024 x IMT loads</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Breakeven tonnage — most favourable case</t>
-        </is>
-      </c>
-      <c r="B6" s="20">
-        <f>IF(COUNT(Breakeven!F8:F25)=0,"",MIN(Breakeven!F8:F25))</f>
+          <t>Breakeven as % of ALL corridor freight — best case</t>
+        </is>
+      </c>
+      <c r="B6" s="19">
+        <f>IF(OR(B5="",B5=0,COUNT(Breakeven!F8:F25)=0),"",MIN(Breakeven!F8:F25)/B5)</f>
         <v/>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>t / yr</t>
+          <t>%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Breakeven sheet</t>
+          <t>derived</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Breakeven tonnage — least favourable case</t>
-        </is>
-      </c>
-      <c r="B7" s="20">
-        <f>IF(COUNT(Breakeven!F8:F25)=0,"",MAX(Breakeven!F8:F25))</f>
+          <t>Breakeven as % of ALL corridor freight — worst case</t>
+        </is>
+      </c>
+      <c r="B7" s="19">
+        <f>IF(OR(B5="",B5=0,COUNT(Breakeven!F8:F25)=0),"",MAX(Breakeven!F8:F25)/B5)</f>
         <v/>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>t / yr</t>
+          <t>%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Breakeven sheet</t>
+          <t>derived</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Ratio: divertible / breakeven (favourable)</t>
-        </is>
-      </c>
-      <c r="B8" s="22">
-        <f>IF(OR(B5="",B6="",B6=0),"",B5/B6)</f>
+          <t>Divertible tonnage (bottom-up, commodity)</t>
+        </is>
+      </c>
+      <c r="B8" s="19">
+        <f>Commodity!E15</f>
         <v/>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>t / yr</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Commodity sheet</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Ratio: divertible / breakeven (unfavourable)</t>
-        </is>
-      </c>
-      <c r="B9" s="22">
-        <f>IF(OR(B5="",B7="",B7=0),"",B5/B7)</f>
+          <t>Breakeven tonnage — most favourable case</t>
+        </is>
+      </c>
+      <c r="B9" s="19">
+        <f>IF(COUNT(Breakeven!F8:F25)=0,"",MIN(Breakeven!F8:F25))</f>
         <v/>
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>t / yr</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Breakeven sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Breakeven tonnage — least favourable case</t>
+        </is>
+      </c>
+      <c r="B10" s="19">
+        <f>IF(COUNT(Breakeven!F8:F25)=0,"",MAX(Breakeven!F8:F25))</f>
+        <v/>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>t / yr</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Breakeven sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Ratio: divertible / breakeven (favourable)</t>
+        </is>
+      </c>
+      <c r="B11" s="15">
+        <f>IF(OR(B8="",B9="",B9=0),"",B8/B9)</f>
+        <v/>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
           <t>x</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>VERDICT GATE</t>
-        </is>
-      </c>
+      <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>Ratio: divertible / breakeven (unfavourable)</t>
+        </is>
+      </c>
+      <c r="B12" s="15">
+        <f>IF(OR(B8="",B10="",B10=0),"",B8/B10)</f>
+        <v/>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>VERDICT GATE</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>Stop Rule 3 test</t>
         </is>
       </c>
-      <c r="B12" s="25">
-        <f>IF(OR(B8="",B9=""),"pending inputs",IF(AND(B8&gt;1,B9&lt;1),"INDETERMINATE — scenarios straddle breakeven; field reconnaissance required",IF(B8&lt;1,"FAILS under every capital scenario",IF(B9&gt;1,"CLEARS under every capital scenario","review"))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="B15" s="24">
+        <f>IF(OR(B11="",B12=""),"pending commodity segregation — see B6:B7 for the all-freight comparison",IF(AND(B11&gt;1,B12&lt;1),"INDETERMINATE — scenarios straddle breakeven; field reconnaissance required",IF(B11&lt;1,"FAILS under every capital scenario",IF(B12&gt;1,"CLEARS under every capital scenario","review"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>A straddle is a real result, not a failure to decide. Per the brief, do not select a base case and present a conclusion — report the scenario at which the answer flips.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Rows 6-7 are the comparison that does NOT wait on commodity segregation: breakeven tonnage as a share of ALL articulated freight in the corridor. Since divertible tonnage cannot exceed total tonnage, those percentages are a LOWER BOUND on the capture rate required — and they assume structures cost zero.</t>
         </is>
       </c>
     </row>
